--- a/models/demo-target/demo-target.xlsx
+++ b/models/demo-target/demo-target.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shxie/Projects/anse-models/demo-target/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shxie/projects/anse-models/demo-target/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E35F1DC-25B9-2F46-8BC4-A6F2E41B4274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5A3652-D2FE-274A-B0F9-DC69A05B5674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22460" yWindow="600" windowWidth="28740" windowHeight="26980" xr2:uid="{73351A0E-E394-C94F-8AB9-3EA9DA143F24}"/>
+    <workbookView xWindow="25600" yWindow="600" windowWidth="25600" windowHeight="26880" activeTab="1" xr2:uid="{73351A0E-E394-C94F-8AB9-3EA9DA143F24}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs - Flow Network" sheetId="1" r:id="rId1"/>
@@ -645,10 +645,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="123">
-  <si>
-    <t>COMMENT</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="119">
   <si>
     <t>Keyword: POOL</t>
   </si>
@@ -807,15 +804,6 @@
   </si>
   <si>
     <t>INITIAL_CMO</t>
-  </si>
-  <si>
-    <t>IPCC default-paper</t>
-  </si>
-  <si>
-    <t>IPCC default-sawnwood</t>
-  </si>
-  <si>
-    <t>IPCC default-panels</t>
   </si>
   <si>
     <t>Keyword: PHYSICAL_STATE</t>
@@ -1444,7 +1432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F935C300-5F44-C54A-ADD4-2A504DCCAD49}">
-  <dimension ref="A1:L66"/>
+  <dimension ref="B1:L61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="7.5703125" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="13.140625" customWidth="1"/>
@@ -1463,46 +1451,46 @@
   <sheetData>
     <row r="1" spans="2:12" s="1" customFormat="1" ht="16" customHeight="1">
       <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="3" spans="2:12" ht="16" customHeight="1">
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="str">
-        <f>"Roundwood, "&amp;'Inputs - Spatial'!$C$10</f>
-        <v>Roundwood, CA</v>
+        <f>"Structural building materials, "&amp;'Inputs - Spatial'!$C$10</f>
+        <v>Structural building materials, CA</v>
       </c>
       <c r="D3">
         <f>'Inputs - Spatial'!$C$2</f>
@@ -1511,68 +1499,75 @@
     </row>
     <row r="4" spans="2:12" ht="16" customHeight="1">
       <c r="B4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" t="str">
-        <f>"Sawnwood, "&amp;'Inputs - Spatial'!$C$10</f>
-        <v>Sawnwood, CA</v>
+        <f>"Residential Dwellings, "&amp;'Inputs - Spatial'!$C$10</f>
+        <v>Residential Dwellings, CA</v>
       </c>
       <c r="D4">
         <f>'Inputs - Spatial'!$C$2</f>
         <v>1</v>
       </c>
-      <c r="E4" t="s">
-        <v>55</v>
+      <c r="E4" t="str">
+        <f>'Inputs - Advanced Curves'!$C$9</f>
+        <v>US Residential Gamma Retention</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="16" customHeight="1">
       <c r="B5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" t="str">
-        <f>"Panels, "&amp;'Inputs - Spatial'!$C$10</f>
-        <v>Panels, CA</v>
+        <f>"Repair &amp; Remodeling, "&amp;'Inputs - Spatial'!$C$10</f>
+        <v>Repair &amp; Remodeling, CA</v>
       </c>
       <c r="D5">
         <f>'Inputs - Spatial'!$C$2</f>
         <v>1</v>
       </c>
-      <c r="E5" t="s">
-        <v>56</v>
+      <c r="E5" t="str">
+        <f>'Inputs - Advanced Curves'!$C$9</f>
+        <v>US Residential Gamma Retention</v>
       </c>
     </row>
     <row r="6" spans="2:12" ht="16" customHeight="1">
       <c r="B6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" t="str">
-        <f>"Paper, "&amp;'Inputs - Spatial'!$C$10</f>
-        <v>Paper, CA</v>
+        <f>"Non-residential building, "&amp;'Inputs - Spatial'!$C$10</f>
+        <v>Non-residential building, CA</v>
       </c>
       <c r="D6">
         <f>'Inputs - Spatial'!$C$2</f>
         <v>1</v>
       </c>
-      <c r="E6" t="s">
-        <v>54</v>
+      <c r="E6" t="str">
+        <f>'Inputs - Advanced Curves'!$C$9</f>
+        <v>US Residential Gamma Retention</v>
       </c>
     </row>
     <row r="8" spans="2:12" ht="16" customHeight="1">
       <c r="B8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="4" t="str">
-        <f>"Bioenergy, "&amp;'Inputs - Spatial'!$C$10</f>
-        <v>Bioenergy, CA</v>
+        <f>"Other Structural Uses, "&amp;'Inputs - Spatial'!$C$10</f>
+        <v>Other Structural Uses, CA</v>
       </c>
       <c r="D8">
         <f>'Inputs - Spatial'!$C$2</f>
         <v>1</v>
       </c>
+      <c r="E8" t="str">
+        <f>'Inputs - Advanced Curves'!$C$9</f>
+        <v>US Residential Gamma Retention</v>
+      </c>
     </row>
     <row r="10" spans="2:12" ht="16" customHeight="1">
       <c r="B10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C10" t="str">
         <f>"CO2, "&amp;'Inputs - Spatial'!$C$10</f>
@@ -1585,46 +1580,46 @@
     </row>
     <row r="12" spans="2:12" s="3" customFormat="1" ht="16" customHeight="1">
       <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="E12" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="F12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H12" s="3" t="s">
+      <c r="I12" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J12" s="3" t="s">
+      <c r="K12" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="K12" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="L12" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="16" customHeight="1">
       <c r="B14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C14" t="str">
-        <f>"Manufacturing, "&amp;'Inputs - Spatial'!C10</f>
-        <v>Manufacturing, CA</v>
+        <f>"Construction Demand, "&amp;'Inputs - Spatial'!C10</f>
+        <v>Construction Demand, CA</v>
       </c>
       <c r="D14" t="str">
         <f>C20</f>
@@ -1637,7 +1632,7 @@
     </row>
     <row r="15" spans="2:12" ht="16" customHeight="1">
       <c r="B15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" t="str">
         <f>"Landfilling, "&amp;'Inputs - Spatial'!$C$10</f>
@@ -1654,7 +1649,7 @@
     </row>
     <row r="16" spans="2:12" ht="16" customHeight="1">
       <c r="B16" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C16" t="str">
         <f>"Combusting, "&amp;'Inputs - Spatial'!$C$10</f>
@@ -1671,67 +1666,67 @@
     </row>
     <row r="18" spans="2:7" s="3" customFormat="1" ht="16" customHeight="1">
       <c r="B18" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="20" spans="2:7" ht="16" customHeight="1">
       <c r="B20" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C20" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="16" customHeight="1">
       <c r="B21" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="16" customHeight="1">
       <c r="B22" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="25" spans="2:7" s="3" customFormat="1" ht="16" customHeight="1">
       <c r="B25" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F25" s="2" t="s">
+      <c r="G25" s="3" t="s">
         <v>28</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="27" spans="2:7" ht="16" customHeight="1">
       <c r="B27" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C27" t="str">
         <f>$C$14</f>
-        <v>Manufacturing, CA</v>
+        <v>Construction Demand, CA</v>
       </c>
       <c r="D27" t="str">
         <f>C3</f>
-        <v>Roundwood, CA</v>
+        <v>Structural building materials, CA</v>
       </c>
       <c r="E27" t="b">
         <v>1</v>
@@ -1742,15 +1737,15 @@
     </row>
     <row r="28" spans="2:7" ht="16" customHeight="1">
       <c r="B28" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" ref="C28:C31" si="0">$C$14</f>
-        <v>Manufacturing, CA</v>
+        <v>Construction Demand, CA</v>
       </c>
       <c r="D28" t="str">
         <f>C4</f>
-        <v>Sawnwood, CA</v>
+        <v>Residential Dwellings, CA</v>
       </c>
       <c r="E28" t="b">
         <v>0</v>
@@ -1761,15 +1756,15 @@
     </row>
     <row r="29" spans="2:7" ht="16" customHeight="1">
       <c r="B29" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
-        <v>Manufacturing, CA</v>
+        <v>Construction Demand, CA</v>
       </c>
       <c r="D29" t="str">
         <f>C5</f>
-        <v>Panels, CA</v>
+        <v>Repair &amp; Remodeling, CA</v>
       </c>
       <c r="E29" t="b">
         <v>0</v>
@@ -1780,15 +1775,15 @@
     </row>
     <row r="30" spans="2:7" ht="16" customHeight="1">
       <c r="B30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
-        <v>Manufacturing, CA</v>
+        <v>Construction Demand, CA</v>
       </c>
       <c r="D30" t="str">
         <f>C6</f>
-        <v>Paper, CA</v>
+        <v>Non-residential building, CA</v>
       </c>
       <c r="E30" t="b">
         <v>0</v>
@@ -1799,15 +1794,15 @@
     </row>
     <row r="31" spans="2:7" ht="16" customHeight="1">
       <c r="B31" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="0"/>
-        <v>Manufacturing, CA</v>
+        <v>Construction Demand, CA</v>
       </c>
       <c r="D31" t="str">
         <f>C8</f>
-        <v>Bioenergy, CA</v>
+        <v>Other Structural Uses, CA</v>
       </c>
       <c r="E31" t="b">
         <v>0</v>
@@ -1818,7 +1813,7 @@
     </row>
     <row r="33" spans="2:10" ht="16" customHeight="1">
       <c r="B33" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C33" t="str" cm="1">
         <f t="array" ref="C33">$C$15</f>
@@ -1826,7 +1821,7 @@
       </c>
       <c r="D33" t="str">
         <f>C4</f>
-        <v>Sawnwood, CA</v>
+        <v>Residential Dwellings, CA</v>
       </c>
       <c r="E33" t="b">
         <v>1</v>
@@ -1837,7 +1832,7 @@
     </row>
     <row r="34" spans="2:10" ht="16" customHeight="1">
       <c r="B34" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C34" t="str" cm="1">
         <f t="array" ref="C34">$C$15</f>
@@ -1845,7 +1840,7 @@
       </c>
       <c r="D34" t="str">
         <f>C5</f>
-        <v>Panels, CA</v>
+        <v>Repair &amp; Remodeling, CA</v>
       </c>
       <c r="E34" t="b">
         <v>1</v>
@@ -1856,7 +1851,7 @@
     </row>
     <row r="35" spans="2:10" ht="16" customHeight="1">
       <c r="B35" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C35" t="str" cm="1">
         <f t="array" ref="C35">$C$15</f>
@@ -1864,7 +1859,7 @@
       </c>
       <c r="D35" t="str">
         <f>C6</f>
-        <v>Paper, CA</v>
+        <v>Non-residential building, CA</v>
       </c>
       <c r="E35" t="b">
         <v>1</v>
@@ -1875,7 +1870,7 @@
     </row>
     <row r="36" spans="2:10" ht="16" customHeight="1">
       <c r="B36" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C36" t="str" cm="1">
         <f t="array" ref="C36">$C$15</f>
@@ -1894,7 +1889,7 @@
     </row>
     <row r="38" spans="2:10" ht="16" customHeight="1">
       <c r="B38" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C38" t="str">
         <f>$C$16</f>
@@ -1902,7 +1897,7 @@
       </c>
       <c r="D38" t="str">
         <f>C8</f>
-        <v>Bioenergy, CA</v>
+        <v>Other Structural Uses, CA</v>
       </c>
       <c r="E38" t="b">
         <v>1</v>
@@ -1913,7 +1908,7 @@
     </row>
     <row r="39" spans="2:10" ht="16" customHeight="1">
       <c r="B39" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C39" t="str">
         <f>$C$16</f>
@@ -1932,30 +1927,30 @@
     </row>
     <row r="41" spans="2:10" s="3" customFormat="1" ht="16" customHeight="1">
       <c r="B41" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D41" s="2" t="s">
+      <c r="E41" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F41" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F41" s="3" t="s">
+      <c r="G41" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="G41" s="3" t="s">
+      <c r="H41" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="43" spans="2:10" ht="16" customHeight="1">
       <c r="B43" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C43" t="str">
         <f>"Commodity Demand, "&amp;'Inputs - Spatial'!$C$10</f>
@@ -1972,7 +1967,7 @@
     </row>
     <row r="44" spans="2:10" ht="16" customHeight="1">
       <c r="B44" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C44" t="str">
         <f>"Landfill Parameters, "&amp;'Inputs - Spatial'!$C$10</f>
@@ -1989,7 +1984,7 @@
     </row>
     <row r="45" spans="2:10" ht="16" customHeight="1">
       <c r="B45" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C45" t="str">
         <f>"Combustion Parameters, "&amp;'Inputs - Spatial'!$C$10</f>
@@ -2006,39 +2001,36 @@
     </row>
     <row r="47" spans="2:10" s="3" customFormat="1" ht="16" customHeight="1">
       <c r="B47" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C47" s="2" t="s">
+      <c r="D47" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="E47" s="2" t="s">
+      <c r="F47" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="G47" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="H47" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="H47" s="3" t="s">
+      <c r="I47" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="I47" s="3" t="s">
+      <c r="J47" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="J47" s="3" t="s">
+    </row>
+    <row r="49" spans="2:6" ht="16" customHeight="1">
+      <c r="B49" t="s">
         <v>45</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="16" customHeight="1">
-      <c r="A49" t="s">
-        <v>0</v>
-      </c>
-      <c r="B49" t="s">
-        <v>46</v>
       </c>
       <c r="C49" t="str">
         <f>$C$43</f>
@@ -2049,272 +2041,148 @@
         <v>1</v>
       </c>
       <c r="F49">
-        <f>'Inputs - Carbon Mass'!F40</f>
-        <v>9100636.3300000001</v>
-      </c>
-      <c r="G49" t="str">
-        <f>'Inputs - Categorical'!C4</f>
-        <v>Sawnwood</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="16" customHeight="1">
-      <c r="A50" t="s">
-        <v>0</v>
-      </c>
+        <v>30</v>
+      </c>
+    </row>
+    <row r="50" spans="2:6" ht="16" customHeight="1">
       <c r="B50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C50" t="str">
         <f t="shared" ref="C50:C52" si="1">$C$43</f>
         <v>Commodity Demand, CA</v>
       </c>
       <c r="D50">
-        <f>F29</f>
+        <f t="shared" ref="D50:D52" si="2">F29</f>
         <v>2</v>
       </c>
       <c r="F50">
-        <f>'Inputs - Carbon Mass'!F76</f>
-        <v>1575533</v>
-      </c>
-      <c r="G50" t="str">
-        <f>'Inputs - Categorical'!C5</f>
-        <v>Panels</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="16" customHeight="1">
-      <c r="A51" t="s">
-        <v>0</v>
-      </c>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="2:6" ht="16" customHeight="1">
       <c r="B51" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C51" t="str">
         <f t="shared" si="1"/>
         <v>Commodity Demand, CA</v>
       </c>
       <c r="D51">
-        <f>F30</f>
+        <f t="shared" si="2"/>
         <v>3</v>
       </c>
       <c r="F51">
-        <f>'Inputs - Carbon Mass'!F112</f>
-        <v>6458552</v>
-      </c>
-      <c r="G51" t="str">
-        <f>'Inputs - Categorical'!C6</f>
-        <v>Paper</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="16" customHeight="1">
-      <c r="A52" t="s">
-        <v>0</v>
-      </c>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="52" spans="2:6" ht="16" customHeight="1">
       <c r="B52" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C52" t="str">
         <f t="shared" si="1"/>
         <v>Commodity Demand, CA</v>
       </c>
       <c r="D52">
-        <f>F31</f>
+        <f t="shared" si="2"/>
         <v>4</v>
       </c>
       <c r="F52">
         <v>0</v>
       </c>
-      <c r="G52" t="str">
-        <f>'Inputs - Categorical'!C7</f>
-        <v>Bioenergy</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="16" customHeight="1">
+    </row>
+    <row r="54" spans="2:6" ht="16" customHeight="1">
       <c r="B54" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C54" t="str">
         <f>$C$43</f>
         <v>Commodity Demand, CA</v>
       </c>
       <c r="D54">
-        <f>F28</f>
+        <f t="shared" ref="D54:D57" si="3">F28</f>
         <v>1</v>
       </c>
-      <c r="F54">
-        <v>100</v>
-      </c>
-      <c r="G54" t="str">
-        <f>'Inputs - Categorical'!C4</f>
-        <v>Sawnwood</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="16" customHeight="1">
+      <c r="E54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:6" ht="16" customHeight="1">
       <c r="B55" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C55" t="str">
-        <f t="shared" ref="C55:C57" si="2">$C$43</f>
+        <f t="shared" ref="C55:C57" si="4">$C$43</f>
         <v>Commodity Demand, CA</v>
       </c>
       <c r="D55">
-        <f t="shared" ref="D55:D57" si="3">F29</f>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="F55">
-        <v>50</v>
-      </c>
-      <c r="G55" t="str">
-        <f>'Inputs - Categorical'!C5</f>
-        <v>Panels</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="16" customHeight="1">
+      <c r="E55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:6" ht="16" customHeight="1">
       <c r="B56" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C56" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Commodity Demand, CA</v>
       </c>
       <c r="D56">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="F56">
-        <v>50</v>
-      </c>
-      <c r="G56" t="str">
-        <f>'Inputs - Categorical'!C6</f>
-        <v>Paper</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="16" customHeight="1">
+      <c r="E56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:6" ht="16" customHeight="1">
       <c r="B57" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C57" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v>Commodity Demand, CA</v>
       </c>
       <c r="D57">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="F57">
-        <v>0</v>
-      </c>
-      <c r="G57" t="str">
-        <f>'Inputs - Categorical'!C7</f>
-        <v>Bioenergy</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="16" customHeight="1">
+      <c r="E57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="2:6" ht="16" customHeight="1">
       <c r="B59" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C59" t="str">
-        <f>$C$43</f>
-        <v>Commodity Demand, CA</v>
-      </c>
-      <c r="D59">
-        <f t="shared" ref="D59:D62" si="4">F28</f>
-        <v>1</v>
-      </c>
-      <c r="E59">
-        <v>0</v>
-      </c>
-      <c r="G59" t="str">
-        <f>'Inputs - Categorical'!C4</f>
-        <v>Sawnwood</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="16" customHeight="1">
-      <c r="B60" t="s">
-        <v>46</v>
-      </c>
-      <c r="C60" t="str">
-        <f t="shared" ref="C60:C62" si="5">$C$43</f>
-        <v>Commodity Demand, CA</v>
-      </c>
-      <c r="D60">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="E60">
-        <v>0</v>
-      </c>
-      <c r="G60" t="str">
-        <f>'Inputs - Categorical'!C5</f>
-        <v>Panels</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="16" customHeight="1">
-      <c r="B61" t="s">
-        <v>46</v>
-      </c>
-      <c r="C61" t="str">
-        <f t="shared" si="5"/>
-        <v>Commodity Demand, CA</v>
-      </c>
-      <c r="D61">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="E61">
-        <v>0</v>
-      </c>
-      <c r="G61" t="str">
-        <f>'Inputs - Categorical'!C6</f>
-        <v>Paper</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="16" customHeight="1">
-      <c r="B62" t="s">
-        <v>46</v>
-      </c>
-      <c r="C62" t="str">
-        <f t="shared" si="5"/>
-        <v>Commodity Demand, CA</v>
-      </c>
-      <c r="D62">
-        <f t="shared" si="4"/>
-        <v>4</v>
-      </c>
-      <c r="E62">
-        <v>1</v>
-      </c>
-      <c r="G62" t="str">
-        <f>'Inputs - Categorical'!C7</f>
-        <v>Bioenergy</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="16" customHeight="1">
-      <c r="B64" t="s">
-        <v>46</v>
-      </c>
-      <c r="C64" t="str">
         <f>C45</f>
         <v>Combustion Parameters, CA</v>
       </c>
-      <c r="D64">
+      <c r="D59">
         <v>1</v>
       </c>
-      <c r="E64">
+      <c r="E59">
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="2:5" ht="16" customHeight="1">
-      <c r="B66" t="s">
-        <v>46</v>
-      </c>
-      <c r="C66" t="str" cm="1">
-        <f t="array" ref="C66">C44</f>
+    <row r="61" spans="2:6" ht="16" customHeight="1">
+      <c r="B61" t="s">
+        <v>45</v>
+      </c>
+      <c r="C61" t="str" cm="1">
+        <f t="array" ref="C61">C44</f>
         <v>Landfill Parameters, CA</v>
       </c>
-      <c r="D66">
+      <c r="D61">
         <v>1</v>
       </c>
-      <c r="E66">
+      <c r="E61">
         <v>1</v>
       </c>
     </row>
@@ -2327,11 +2195,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22152807-D21A-1A49-9C05-E8FAC8B5CEA8}">
-  <dimension ref="A1:K146"/>
+  <dimension ref="B1:K2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="2" max="2" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="26.5703125" customWidth="1"/>
     <col min="4" max="4" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.5703125" bestFit="1" customWidth="1"/>
@@ -2340,2994 +2208,51 @@
     <col min="11" max="11" width="10.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1">
+    <row r="1" spans="2:11" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="I1" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="2:11">
+      <c r="B2" t="s">
         <v>52</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="B2" t="s">
-        <v>53</v>
       </c>
       <c r="C2" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
+        <v>Structural building materials, CA</v>
       </c>
       <c r="F2">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="G2">
         <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1990</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F3">
-        <v>37127083</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1990</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
-      <c r="A4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F4">
-        <v>36678472</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-      <c r="K4">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
-      <c r="A5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C5" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F5">
-        <v>38905955</v>
-      </c>
-      <c r="G5">
-        <v>3</v>
-      </c>
-      <c r="K5">
-        <v>1992</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
-      <c r="A6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F6">
-        <v>40348197</v>
-      </c>
-      <c r="G6">
-        <v>4</v>
-      </c>
-      <c r="K6">
-        <v>1993</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
-      <c r="A7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" t="s">
-        <v>53</v>
-      </c>
-      <c r="C7" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F7">
-        <v>41958296</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-      <c r="K7">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
-      <c r="A8" t="s">
-        <v>0</v>
-      </c>
-      <c r="B8" t="s">
-        <v>53</v>
-      </c>
-      <c r="C8" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F8">
-        <v>43150928</v>
-      </c>
-      <c r="G8">
-        <v>6</v>
-      </c>
-      <c r="K8">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
-      <c r="A9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C9" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F9">
-        <v>43483436</v>
-      </c>
-      <c r="G9">
-        <v>7</v>
-      </c>
-      <c r="K9">
-        <v>1996</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F10">
-        <v>43752282</v>
-      </c>
-      <c r="G10">
-        <v>8</v>
-      </c>
-      <c r="K10">
-        <v>1997</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C11" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F11">
-        <v>40519718</v>
-      </c>
-      <c r="G11">
-        <v>9</v>
-      </c>
-      <c r="K11">
-        <v>1998</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F12">
-        <v>44400810</v>
-      </c>
-      <c r="G12">
-        <v>10</v>
-      </c>
-      <c r="K12">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13" t="s">
-        <v>0</v>
-      </c>
-      <c r="B13" t="s">
-        <v>53</v>
-      </c>
-      <c r="C13" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F13">
-        <v>46222505</v>
-      </c>
-      <c r="G13">
-        <v>11</v>
-      </c>
-      <c r="K13">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14" t="s">
-        <v>0</v>
-      </c>
-      <c r="B14" t="s">
-        <v>53</v>
-      </c>
-      <c r="C14" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F14">
-        <v>42560337</v>
-      </c>
-      <c r="G14">
-        <v>12</v>
-      </c>
-      <c r="K14">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15" t="s">
-        <v>0</v>
-      </c>
-      <c r="B15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F15">
-        <v>45359633</v>
-      </c>
-      <c r="G15">
-        <v>13</v>
-      </c>
-      <c r="K15">
-        <v>2002</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16" t="s">
-        <v>0</v>
-      </c>
-      <c r="B16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F16">
-        <v>41138018</v>
-      </c>
-      <c r="G16">
-        <v>14</v>
-      </c>
-      <c r="K16">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
-      <c r="A17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B17" t="s">
-        <v>53</v>
-      </c>
-      <c r="C17" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F17">
-        <v>47648717</v>
-      </c>
-      <c r="G17">
-        <v>15</v>
-      </c>
-      <c r="K17">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
-      <c r="A18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B18" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F18">
-        <v>46514709</v>
-      </c>
-      <c r="G18">
-        <v>16</v>
-      </c>
-      <c r="K18">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
-      <c r="A19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F19">
-        <v>42120199</v>
-      </c>
-      <c r="G19">
-        <v>17</v>
-      </c>
-      <c r="K19">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
-      <c r="A20" t="s">
-        <v>0</v>
-      </c>
-      <c r="B20" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F20">
-        <v>37693171</v>
-      </c>
-      <c r="G20">
-        <v>18</v>
-      </c>
-      <c r="K20">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
-      <c r="A21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" t="s">
-        <v>53</v>
-      </c>
-      <c r="C21" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F21">
-        <v>31885044</v>
-      </c>
-      <c r="G21">
-        <v>19</v>
-      </c>
-      <c r="K21">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
-      <c r="A22" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" t="s">
-        <v>53</v>
-      </c>
-      <c r="C22" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F22">
-        <v>26634074</v>
-      </c>
-      <c r="G22">
-        <v>20</v>
-      </c>
-      <c r="K22">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
-      <c r="A23" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" t="s">
-        <v>53</v>
-      </c>
-      <c r="C23" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F23">
-        <v>32520977</v>
-      </c>
-      <c r="G23">
-        <v>21</v>
-      </c>
-      <c r="K23">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
-      <c r="A24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B24" t="s">
-        <v>53</v>
-      </c>
-      <c r="C24" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F24">
-        <v>33932796.350000001</v>
-      </c>
-      <c r="G24">
-        <v>22</v>
-      </c>
-      <c r="K24">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
-      <c r="A25" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F25">
-        <v>33933907</v>
-      </c>
-      <c r="G25">
-        <v>23</v>
-      </c>
-      <c r="K25">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
-      <c r="A26" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C26" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F26">
-        <v>34825414.534000002</v>
-      </c>
-      <c r="G26">
-        <v>24</v>
-      </c>
-      <c r="K26">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
-      <c r="A27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B27" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F27">
-        <v>35143340.958999999</v>
-      </c>
-      <c r="G27">
-        <v>25</v>
-      </c>
-      <c r="K27">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
-      <c r="A28" t="s">
-        <v>0</v>
-      </c>
-      <c r="B28" t="s">
-        <v>53</v>
-      </c>
-      <c r="C28" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F28">
-        <v>35723207.660000004</v>
-      </c>
-      <c r="G28">
-        <v>26</v>
-      </c>
-      <c r="K28">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
-      <c r="A29" t="s">
-        <v>0</v>
-      </c>
-      <c r="B29" t="s">
-        <v>53</v>
-      </c>
-      <c r="C29" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F29">
-        <v>35894376</v>
-      </c>
-      <c r="G29">
-        <v>27</v>
-      </c>
-      <c r="K29">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
-      <c r="A30" t="s">
-        <v>0</v>
-      </c>
-      <c r="B30" t="s">
-        <v>53</v>
-      </c>
-      <c r="C30" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F30">
-        <v>35888193</v>
-      </c>
-      <c r="G30">
-        <v>28</v>
-      </c>
-      <c r="K30">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
-      <c r="A31" t="s">
-        <v>0</v>
-      </c>
-      <c r="B31" t="s">
-        <v>53</v>
-      </c>
-      <c r="C31" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F31">
-        <v>35907843.947999999</v>
-      </c>
-      <c r="G31">
-        <v>29</v>
-      </c>
-      <c r="K31">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
-      <c r="A32" t="s">
-        <v>0</v>
-      </c>
-      <c r="B32" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F32">
-        <v>32447111.447000001</v>
-      </c>
-      <c r="G32">
-        <v>30</v>
-      </c>
-      <c r="K32">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
-      <c r="A33" t="s">
-        <v>0</v>
-      </c>
-      <c r="B33" t="s">
-        <v>53</v>
-      </c>
-      <c r="C33" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F33">
-        <v>32663199.740000002</v>
-      </c>
-      <c r="G33">
-        <v>31</v>
-      </c>
-      <c r="K33">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
-      <c r="A34" t="s">
-        <v>0</v>
-      </c>
-      <c r="B34" t="s">
-        <v>53</v>
-      </c>
-      <c r="C34" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F34">
-        <v>33352126.546</v>
-      </c>
-      <c r="G34">
-        <v>32</v>
-      </c>
-      <c r="K34">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
-      <c r="A35" t="s">
-        <v>0</v>
-      </c>
-      <c r="B35" t="s">
-        <v>53</v>
-      </c>
-      <c r="C35" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F35">
-        <v>33352126.546</v>
-      </c>
-      <c r="G35">
-        <v>33</v>
-      </c>
-      <c r="K35">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
-      <c r="A36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B36" t="s">
-        <v>53</v>
-      </c>
-      <c r="C36" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F36">
-        <v>26583833.232000001</v>
-      </c>
-      <c r="G36">
-        <v>34</v>
-      </c>
-      <c r="K36">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
-      <c r="A37" t="s">
-        <v>0</v>
-      </c>
-      <c r="B37" t="s">
-        <v>53</v>
-      </c>
-      <c r="C37" t="str">
-        <f>'Inputs - Flow Network'!$C$3</f>
-        <v>Roundwood, CA</v>
-      </c>
-      <c r="F37">
-        <v>26583833.232000001</v>
-      </c>
-      <c r="G37">
-        <v>35</v>
-      </c>
-      <c r="K37">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
-      <c r="A40" t="s">
-        <v>0</v>
-      </c>
-      <c r="B40" t="s">
-        <v>53</v>
-      </c>
-      <c r="C40" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F40">
-        <v>9100636.3300000001</v>
-      </c>
-      <c r="G40">
-        <v>1</v>
-      </c>
-      <c r="K40">
-        <v>1990</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
-      <c r="A41" t="s">
-        <v>0</v>
-      </c>
-      <c r="B41" t="s">
-        <v>53</v>
-      </c>
-      <c r="C41" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F41">
-        <v>8583184.0370000005</v>
-      </c>
-      <c r="G41">
-        <v>2</v>
-      </c>
-      <c r="K41">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
-      <c r="A42" t="s">
-        <v>0</v>
-      </c>
-      <c r="B42" t="s">
-        <v>53</v>
-      </c>
-      <c r="C42" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F42">
-        <v>9191597.8780000005</v>
-      </c>
-      <c r="G42">
-        <v>3</v>
-      </c>
-      <c r="K42">
-        <v>1992</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
-      <c r="A43" t="s">
-        <v>0</v>
-      </c>
-      <c r="B43" t="s">
-        <v>53</v>
-      </c>
-      <c r="C43" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F43">
-        <v>9897099.0170000009</v>
-      </c>
-      <c r="G43">
-        <v>4</v>
-      </c>
-      <c r="K43">
-        <v>1993</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
-      <c r="A44" t="s">
-        <v>0</v>
-      </c>
-      <c r="B44" t="s">
-        <v>53</v>
-      </c>
-      <c r="C44" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F44">
-        <v>10328936.912</v>
-      </c>
-      <c r="G44">
-        <v>5</v>
-      </c>
-      <c r="K44">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
-      <c r="A45" t="s">
-        <v>0</v>
-      </c>
-      <c r="B45" t="s">
-        <v>53</v>
-      </c>
-      <c r="C45" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F45">
-        <v>10406683.328</v>
-      </c>
-      <c r="G45">
-        <v>6</v>
-      </c>
-      <c r="K45">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
-      <c r="A46" t="s">
-        <v>0</v>
-      </c>
-      <c r="B46" t="s">
-        <v>53</v>
-      </c>
-      <c r="C46" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F46">
-        <v>10768727.061000001</v>
-      </c>
-      <c r="G46">
-        <v>7</v>
-      </c>
-      <c r="K46">
-        <v>1996</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
-      <c r="A47" t="s">
-        <v>0</v>
-      </c>
-      <c r="B47" t="s">
-        <v>53</v>
-      </c>
-      <c r="C47" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F47">
-        <v>10915189.736</v>
-      </c>
-      <c r="G47">
-        <v>8</v>
-      </c>
-      <c r="K47">
-        <v>1997</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
-      <c r="A48" t="s">
-        <v>0</v>
-      </c>
-      <c r="B48" t="s">
-        <v>53</v>
-      </c>
-      <c r="C48" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F48">
-        <v>10805425.685000001</v>
-      </c>
-      <c r="G48">
-        <v>9</v>
-      </c>
-      <c r="K48">
-        <v>1998</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
-      <c r="A49" t="s">
-        <v>0</v>
-      </c>
-      <c r="B49" t="s">
-        <v>53</v>
-      </c>
-      <c r="C49" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F49">
-        <v>11544297.391000001</v>
-      </c>
-      <c r="G49">
-        <v>10</v>
-      </c>
-      <c r="K49">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
-      <c r="A50" t="s">
-        <v>0</v>
-      </c>
-      <c r="B50" t="s">
-        <v>53</v>
-      </c>
-      <c r="C50" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F50">
-        <v>11556395.003</v>
-      </c>
-      <c r="G50">
-        <v>11</v>
-      </c>
-      <c r="K50">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
-      <c r="A51" t="s">
-        <v>0</v>
-      </c>
-      <c r="B51" t="s">
-        <v>53</v>
-      </c>
-      <c r="C51" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F51">
-        <v>12299040.4</v>
-      </c>
-      <c r="G51">
-        <v>12</v>
-      </c>
-      <c r="K51">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
-      <c r="A52" t="s">
-        <v>0</v>
-      </c>
-      <c r="B52" t="s">
-        <v>53</v>
-      </c>
-      <c r="C52" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F52">
-        <v>13392212.204</v>
-      </c>
-      <c r="G52">
-        <v>13</v>
-      </c>
-      <c r="K52">
-        <v>2002</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
-      <c r="A53" t="s">
-        <v>0</v>
-      </c>
-      <c r="B53" t="s">
-        <v>53</v>
-      </c>
-      <c r="C53" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F53">
-        <v>13028213.498</v>
-      </c>
-      <c r="G53">
-        <v>14</v>
-      </c>
-      <c r="K53">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
-      <c r="A54" t="s">
-        <v>0</v>
-      </c>
-      <c r="B54" t="s">
-        <v>53</v>
-      </c>
-      <c r="C54" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F54">
-        <v>13957987.390000001</v>
-      </c>
-      <c r="G54">
-        <v>15</v>
-      </c>
-      <c r="K54">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
-      <c r="A55" t="s">
-        <v>0</v>
-      </c>
-      <c r="B55" t="s">
-        <v>53</v>
-      </c>
-      <c r="C55" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F55">
-        <v>13782738.728</v>
-      </c>
-      <c r="G55">
-        <v>16</v>
-      </c>
-      <c r="K55">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
-      <c r="A56" t="s">
-        <v>0</v>
-      </c>
-      <c r="B56" t="s">
-        <v>53</v>
-      </c>
-      <c r="C56" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F56">
-        <v>13444408.632000001</v>
-      </c>
-      <c r="G56">
-        <v>17</v>
-      </c>
-      <c r="K56">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
-      <c r="A57" t="s">
-        <v>0</v>
-      </c>
-      <c r="B57" t="s">
-        <v>53</v>
-      </c>
-      <c r="C57" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F57">
-        <v>11973135.157</v>
-      </c>
-      <c r="G57">
-        <v>18</v>
-      </c>
-      <c r="K57">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
-      <c r="A58" t="s">
-        <v>0</v>
-      </c>
-      <c r="B58" t="s">
-        <v>53</v>
-      </c>
-      <c r="C58" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F58">
-        <v>9514405.438000001</v>
-      </c>
-      <c r="G58">
-        <v>19</v>
-      </c>
-      <c r="K58">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
-      <c r="A59" t="s">
-        <v>0</v>
-      </c>
-      <c r="B59" t="s">
-        <v>53</v>
-      </c>
-      <c r="C59" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F59">
-        <v>7515672.3700000001</v>
-      </c>
-      <c r="G59">
-        <v>20</v>
-      </c>
-      <c r="K59">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
-      <c r="A60" t="s">
-        <v>0</v>
-      </c>
-      <c r="B60" t="s">
-        <v>53</v>
-      </c>
-      <c r="C60" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F60">
-        <v>8854743</v>
-      </c>
-      <c r="G60">
-        <v>21</v>
-      </c>
-      <c r="K60">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
-      <c r="A61" t="s">
-        <v>0</v>
-      </c>
-      <c r="B61" t="s">
-        <v>53</v>
-      </c>
-      <c r="C61" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F61">
-        <v>8903469.620000001</v>
-      </c>
-      <c r="G61">
-        <v>22</v>
-      </c>
-      <c r="K61">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
-      <c r="A62" t="s">
-        <v>0</v>
-      </c>
-      <c r="B62" t="s">
-        <v>53</v>
-      </c>
-      <c r="C62" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F62">
-        <v>9289165.847000001</v>
-      </c>
-      <c r="G62">
-        <v>23</v>
-      </c>
-      <c r="K62">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
-      <c r="A63" t="s">
-        <v>0</v>
-      </c>
-      <c r="B63" t="s">
-        <v>53</v>
-      </c>
-      <c r="C63" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F63">
-        <v>9804280.7369999997</v>
-      </c>
-      <c r="G63">
-        <v>24</v>
-      </c>
-      <c r="K63">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
-      <c r="A64" t="s">
-        <v>0</v>
-      </c>
-      <c r="B64" t="s">
-        <v>53</v>
-      </c>
-      <c r="C64" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F64">
-        <v>9927379</v>
-      </c>
-      <c r="G64">
-        <v>25</v>
-      </c>
-      <c r="K64">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
-      <c r="A65" t="s">
-        <v>0</v>
-      </c>
-      <c r="B65" t="s">
-        <v>53</v>
-      </c>
-      <c r="C65" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F65">
-        <v>10789302.940000001</v>
-      </c>
-      <c r="G65">
-        <v>26</v>
-      </c>
-      <c r="K65">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11">
-      <c r="A66" t="s">
-        <v>0</v>
-      </c>
-      <c r="B66" t="s">
-        <v>53</v>
-      </c>
-      <c r="C66" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F66">
-        <v>11386727.071</v>
-      </c>
-      <c r="G66">
-        <v>27</v>
-      </c>
-      <c r="K66">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11">
-      <c r="A67" t="s">
-        <v>0</v>
-      </c>
-      <c r="B67" t="s">
-        <v>53</v>
-      </c>
-      <c r="C67" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F67">
-        <v>10960260.6</v>
-      </c>
-      <c r="G67">
-        <v>28</v>
-      </c>
-      <c r="K67">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11">
-      <c r="A68" t="s">
-        <v>0</v>
-      </c>
-      <c r="B68" t="s">
-        <v>53</v>
-      </c>
-      <c r="C68" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F68">
-        <v>10901183.18</v>
-      </c>
-      <c r="G68">
-        <v>29</v>
-      </c>
-      <c r="K68">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11">
-      <c r="A69" t="s">
-        <v>0</v>
-      </c>
-      <c r="B69" t="s">
-        <v>53</v>
-      </c>
-      <c r="C69" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F69">
-        <v>9579550.9000000004</v>
-      </c>
-      <c r="G69">
-        <v>30</v>
-      </c>
-      <c r="K69">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11">
-      <c r="A70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B70" t="s">
-        <v>53</v>
-      </c>
-      <c r="C70" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F70">
-        <v>9250958.8000000007</v>
-      </c>
-      <c r="G70">
-        <v>31</v>
-      </c>
-      <c r="K70">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11">
-      <c r="A71" t="s">
-        <v>0</v>
-      </c>
-      <c r="B71" t="s">
-        <v>53</v>
-      </c>
-      <c r="C71" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F71">
-        <v>9407342.9000000004</v>
-      </c>
-      <c r="G71">
-        <v>32</v>
-      </c>
-      <c r="K71">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11">
-      <c r="A72" t="s">
-        <v>0</v>
-      </c>
-      <c r="B72" t="s">
-        <v>53</v>
-      </c>
-      <c r="C72" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F72">
-        <v>8532265.2000000011</v>
-      </c>
-      <c r="G72">
-        <v>33</v>
-      </c>
-      <c r="K72">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="73" spans="1:11">
-      <c r="A73" t="s">
-        <v>0</v>
-      </c>
-      <c r="B73" t="s">
-        <v>53</v>
-      </c>
-      <c r="C73" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F73">
-        <v>8150119.1600000001</v>
-      </c>
-      <c r="G73">
-        <v>34</v>
-      </c>
-      <c r="K73">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="74" spans="1:11">
-      <c r="A74" t="s">
-        <v>0</v>
-      </c>
-      <c r="B74" t="s">
-        <v>53</v>
-      </c>
-      <c r="C74" t="str">
-        <f>'Inputs - Flow Network'!$C$4</f>
-        <v>Sawnwood, CA</v>
-      </c>
-      <c r="F74">
-        <v>8093244.7200000007</v>
-      </c>
-      <c r="G74">
-        <v>35</v>
-      </c>
-      <c r="K74">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11">
-      <c r="A76" t="s">
-        <v>0</v>
-      </c>
-      <c r="B76" t="s">
-        <v>53</v>
-      </c>
-      <c r="C76" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F76">
-        <v>1575533</v>
-      </c>
-      <c r="G76">
-        <v>1</v>
-      </c>
-      <c r="K76">
-        <v>1990</v>
-      </c>
-    </row>
-    <row r="77" spans="1:11">
-      <c r="A77" t="s">
-        <v>0</v>
-      </c>
-      <c r="B77" t="s">
-        <v>53</v>
-      </c>
-      <c r="C77" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F77">
-        <v>1357643</v>
-      </c>
-      <c r="G77">
-        <v>2</v>
-      </c>
-      <c r="K77">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="78" spans="1:11">
-      <c r="A78" t="s">
-        <v>0</v>
-      </c>
-      <c r="B78" t="s">
-        <v>53</v>
-      </c>
-      <c r="C78" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F78">
-        <v>1632023</v>
-      </c>
-      <c r="G78">
-        <v>3</v>
-      </c>
-      <c r="K78">
-        <v>1992</v>
-      </c>
-    </row>
-    <row r="79" spans="1:11">
-      <c r="A79" t="s">
-        <v>0</v>
-      </c>
-      <c r="B79" t="s">
-        <v>53</v>
-      </c>
-      <c r="C79" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F79">
-        <v>1814943</v>
-      </c>
-      <c r="G79">
-        <v>4</v>
-      </c>
-      <c r="K79">
-        <v>1993</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11">
-      <c r="A80" t="s">
-        <v>0</v>
-      </c>
-      <c r="B80" t="s">
-        <v>53</v>
-      </c>
-      <c r="C80" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F80">
-        <v>1924426.0000000002</v>
-      </c>
-      <c r="G80">
-        <v>5</v>
-      </c>
-      <c r="K80">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11">
-      <c r="A81" t="s">
-        <v>0</v>
-      </c>
-      <c r="B81" t="s">
-        <v>53</v>
-      </c>
-      <c r="C81" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F81">
-        <v>2113264</v>
-      </c>
-      <c r="G81">
-        <v>6</v>
-      </c>
-      <c r="K81">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11">
-      <c r="A82" t="s">
-        <v>0</v>
-      </c>
-      <c r="B82" t="s">
-        <v>53</v>
-      </c>
-      <c r="C82" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F82">
-        <v>2545278</v>
-      </c>
-      <c r="G82">
-        <v>7</v>
-      </c>
-      <c r="K82">
-        <v>1996</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11">
-      <c r="A83" t="s">
-        <v>0</v>
-      </c>
-      <c r="B83" t="s">
-        <v>53</v>
-      </c>
-      <c r="C83" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F83">
-        <v>2915960</v>
-      </c>
-      <c r="G83">
-        <v>8</v>
-      </c>
-      <c r="K83">
-        <v>1997</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11">
-      <c r="A84" t="s">
-        <v>0</v>
-      </c>
-      <c r="B84" t="s">
-        <v>53</v>
-      </c>
-      <c r="C84" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F84">
-        <v>3205142.5320000001</v>
-      </c>
-      <c r="G84">
-        <v>9</v>
-      </c>
-      <c r="K84">
-        <v>1998</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11">
-      <c r="A85" t="s">
-        <v>0</v>
-      </c>
-      <c r="B85" t="s">
-        <v>53</v>
-      </c>
-      <c r="C85" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F85">
-        <v>3792674.5780000002</v>
-      </c>
-      <c r="G85">
-        <v>10</v>
-      </c>
-      <c r="K85">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11">
-      <c r="A86" t="s">
-        <v>0</v>
-      </c>
-      <c r="B86" t="s">
-        <v>53</v>
-      </c>
-      <c r="C86" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F86">
-        <v>3884478.3600000003</v>
-      </c>
-      <c r="G86">
-        <v>11</v>
-      </c>
-      <c r="K86">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11">
-      <c r="A87" t="s">
-        <v>0</v>
-      </c>
-      <c r="B87" t="s">
-        <v>53</v>
-      </c>
-      <c r="C87" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F87">
-        <v>3946499.0000000005</v>
-      </c>
-      <c r="G87">
-        <v>12</v>
-      </c>
-      <c r="K87">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11">
-      <c r="A88" t="s">
-        <v>0</v>
-      </c>
-      <c r="B88" t="s">
-        <v>53</v>
-      </c>
-      <c r="C88" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F88">
-        <v>4140717.0000000005</v>
-      </c>
-      <c r="G88">
-        <v>13</v>
-      </c>
-      <c r="K88">
-        <v>2002</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11">
-      <c r="A89" t="s">
-        <v>0</v>
-      </c>
-      <c r="B89" t="s">
-        <v>53</v>
-      </c>
-      <c r="C89" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F89">
-        <v>4247779</v>
-      </c>
-      <c r="G89">
-        <v>14</v>
-      </c>
-      <c r="K89">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11">
-      <c r="A90" t="s">
-        <v>0</v>
-      </c>
-      <c r="B90" t="s">
-        <v>53</v>
-      </c>
-      <c r="C90" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F90">
-        <v>4239171</v>
-      </c>
-      <c r="G90">
-        <v>15</v>
-      </c>
-      <c r="K90">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11">
-      <c r="A91" t="s">
-        <v>0</v>
-      </c>
-      <c r="B91" t="s">
-        <v>53</v>
-      </c>
-      <c r="C91" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F91">
-        <v>4492569</v>
-      </c>
-      <c r="G91">
-        <v>16</v>
-      </c>
-      <c r="K91">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11">
-      <c r="A92" t="s">
-        <v>0</v>
-      </c>
-      <c r="B92" t="s">
-        <v>53</v>
-      </c>
-      <c r="C92" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F92">
-        <v>4501177</v>
-      </c>
-      <c r="G92">
-        <v>17</v>
-      </c>
-      <c r="K92">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11">
-      <c r="A93" t="s">
-        <v>0</v>
-      </c>
-      <c r="B93" t="s">
-        <v>53</v>
-      </c>
-      <c r="C93" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F93">
-        <v>4582953</v>
-      </c>
-      <c r="G93">
-        <v>18</v>
-      </c>
-      <c r="K93">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11">
-      <c r="A94" t="s">
-        <v>0</v>
-      </c>
-      <c r="B94" t="s">
-        <v>53</v>
-      </c>
-      <c r="C94" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F94">
-        <v>3179580</v>
-      </c>
-      <c r="G94">
-        <v>19</v>
-      </c>
-      <c r="K94">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11">
-      <c r="A95" t="s">
-        <v>0</v>
-      </c>
-      <c r="B95" t="s">
-        <v>53</v>
-      </c>
-      <c r="C95" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F95">
-        <v>2266863</v>
-      </c>
-      <c r="G95">
-        <v>20</v>
-      </c>
-      <c r="K95">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11">
-      <c r="A96" t="s">
-        <v>0</v>
-      </c>
-      <c r="B96" t="s">
-        <v>53</v>
-      </c>
-      <c r="C96" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F96">
-        <v>2433374</v>
-      </c>
-      <c r="G96">
-        <v>21</v>
-      </c>
-      <c r="K96">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11">
-      <c r="A97" t="s">
-        <v>0</v>
-      </c>
-      <c r="B97" t="s">
-        <v>53</v>
-      </c>
-      <c r="C97" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F97">
-        <v>2586435</v>
-      </c>
-      <c r="G97">
-        <v>22</v>
-      </c>
-      <c r="K97">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11">
-      <c r="A98" t="s">
-        <v>0</v>
-      </c>
-      <c r="B98" t="s">
-        <v>53</v>
-      </c>
-      <c r="C98" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F98">
-        <v>2724970</v>
-      </c>
-      <c r="G98">
-        <v>23</v>
-      </c>
-      <c r="K98">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11">
-      <c r="A99" t="s">
-        <v>0</v>
-      </c>
-      <c r="B99" t="s">
-        <v>53</v>
-      </c>
-      <c r="C99" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F99">
-        <v>2865235.477</v>
-      </c>
-      <c r="G99">
-        <v>24</v>
-      </c>
-      <c r="K99">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11">
-      <c r="A100" t="s">
-        <v>0</v>
-      </c>
-      <c r="B100" t="s">
-        <v>53</v>
-      </c>
-      <c r="C100" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F100">
-        <v>3047232</v>
-      </c>
-      <c r="G100">
-        <v>25</v>
-      </c>
-      <c r="K100">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11">
-      <c r="A101" t="s">
-        <v>0</v>
-      </c>
-      <c r="B101" t="s">
-        <v>53</v>
-      </c>
-      <c r="C101" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F101">
-        <v>3168551</v>
-      </c>
-      <c r="G101">
-        <v>26</v>
-      </c>
-      <c r="K101">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11">
-      <c r="A102" t="s">
-        <v>0</v>
-      </c>
-      <c r="B102" t="s">
-        <v>53</v>
-      </c>
-      <c r="C102" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F102">
-        <v>3231492.4270000001</v>
-      </c>
-      <c r="G102">
-        <v>27</v>
-      </c>
-      <c r="K102">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11">
-      <c r="A103" t="s">
-        <v>0</v>
-      </c>
-      <c r="B103" t="s">
-        <v>53</v>
-      </c>
-      <c r="C103" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F103">
-        <v>3330174.27</v>
-      </c>
-      <c r="G103">
-        <v>28</v>
-      </c>
-      <c r="K103">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11">
-      <c r="A104" t="s">
-        <v>0</v>
-      </c>
-      <c r="B104" t="s">
-        <v>53</v>
-      </c>
-      <c r="C104" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F104">
-        <v>3307577.7320000003</v>
-      </c>
-      <c r="G104">
-        <v>29</v>
-      </c>
-      <c r="K104">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11">
-      <c r="A105" t="s">
-        <v>0</v>
-      </c>
-      <c r="B105" t="s">
-        <v>53</v>
-      </c>
-      <c r="C105" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F105">
-        <v>3441969.594</v>
-      </c>
-      <c r="G105">
-        <v>30</v>
-      </c>
-      <c r="K105">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11">
-      <c r="A106" t="s">
-        <v>0</v>
-      </c>
-      <c r="B106" t="s">
-        <v>53</v>
-      </c>
-      <c r="C106" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F106">
-        <v>2960883</v>
-      </c>
-      <c r="G106">
-        <v>31</v>
-      </c>
-      <c r="K106">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11">
-      <c r="A107" t="s">
-        <v>0</v>
-      </c>
-      <c r="B107" t="s">
-        <v>53</v>
-      </c>
-      <c r="C107" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F107">
-        <v>3210427.5750000002</v>
-      </c>
-      <c r="G107">
-        <v>32</v>
-      </c>
-      <c r="K107">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11">
-      <c r="A108" t="s">
-        <v>0</v>
-      </c>
-      <c r="B108" t="s">
-        <v>53</v>
-      </c>
-      <c r="C108" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F108">
-        <v>3167370.8970000003</v>
-      </c>
-      <c r="G108">
-        <v>33</v>
-      </c>
-      <c r="K108">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11">
-      <c r="A109" t="s">
-        <v>0</v>
-      </c>
-      <c r="B109" t="s">
-        <v>53</v>
-      </c>
-      <c r="C109" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F109">
-        <v>2932086.5500000003</v>
-      </c>
-      <c r="G109">
-        <v>34</v>
-      </c>
-      <c r="K109">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11">
-      <c r="A110" t="s">
-        <v>0</v>
-      </c>
-      <c r="B110" t="s">
-        <v>53</v>
-      </c>
-      <c r="C110" t="str">
-        <f>'Inputs - Flow Network'!$C$5</f>
-        <v>Panels, CA</v>
-      </c>
-      <c r="F110">
-        <v>3017020.6100000003</v>
-      </c>
-      <c r="G110">
-        <v>35</v>
-      </c>
-      <c r="K110">
-        <v>2024</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11">
-      <c r="A112" t="s">
-        <v>0</v>
-      </c>
-      <c r="B112" t="s">
-        <v>53</v>
-      </c>
-      <c r="C112" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F112">
-        <v>6458552</v>
-      </c>
-      <c r="G112">
-        <v>1</v>
-      </c>
-      <c r="K112">
-        <v>1990</v>
-      </c>
-    </row>
-    <row r="113" spans="1:11">
-      <c r="A113" t="s">
-        <v>0</v>
-      </c>
-      <c r="B113" t="s">
-        <v>53</v>
-      </c>
-      <c r="C113" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F113">
-        <v>6494450</v>
-      </c>
-      <c r="G113">
-        <v>2</v>
-      </c>
-      <c r="K113">
-        <v>1991</v>
-      </c>
-    </row>
-    <row r="114" spans="1:11">
-      <c r="A114" t="s">
-        <v>0</v>
-      </c>
-      <c r="B114" t="s">
-        <v>53</v>
-      </c>
-      <c r="C114" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F114">
-        <v>6504486</v>
-      </c>
-      <c r="G114">
-        <v>3</v>
-      </c>
-      <c r="K114">
-        <v>1992</v>
-      </c>
-    </row>
-    <row r="115" spans="1:11">
-      <c r="A115" t="s">
-        <v>0</v>
-      </c>
-      <c r="B115" t="s">
-        <v>53</v>
-      </c>
-      <c r="C115" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F115">
-        <v>6879678</v>
-      </c>
-      <c r="G115">
-        <v>4</v>
-      </c>
-      <c r="K115">
-        <v>1993</v>
-      </c>
-    </row>
-    <row r="116" spans="1:11">
-      <c r="A116" t="s">
-        <v>0</v>
-      </c>
-      <c r="B116" t="s">
-        <v>53</v>
-      </c>
-      <c r="C116" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F116">
-        <v>7185004</v>
-      </c>
-      <c r="G116">
-        <v>5</v>
-      </c>
-      <c r="K116">
-        <v>1994</v>
-      </c>
-    </row>
-    <row r="117" spans="1:11">
-      <c r="A117" t="s">
-        <v>0</v>
-      </c>
-      <c r="B117" t="s">
-        <v>53</v>
-      </c>
-      <c r="C117" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F117">
-        <v>7325894</v>
-      </c>
-      <c r="G117">
-        <v>6</v>
-      </c>
-      <c r="K117">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="118" spans="1:11">
-      <c r="A118" t="s">
-        <v>0</v>
-      </c>
-      <c r="B118" t="s">
-        <v>53</v>
-      </c>
-      <c r="C118" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F118">
-        <v>7165704</v>
-      </c>
-      <c r="G118">
-        <v>7</v>
-      </c>
-      <c r="K118">
-        <v>1996</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11">
-      <c r="A119" t="s">
-        <v>0</v>
-      </c>
-      <c r="B119" t="s">
-        <v>53</v>
-      </c>
-      <c r="C119" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F119">
-        <v>7379934</v>
-      </c>
-      <c r="G119">
-        <v>8</v>
-      </c>
-      <c r="K119">
-        <v>1997</v>
-      </c>
-    </row>
-    <row r="120" spans="1:11">
-      <c r="A120" t="s">
-        <v>0</v>
-      </c>
-      <c r="B120" t="s">
-        <v>53</v>
-      </c>
-      <c r="C120" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F120">
-        <v>7285750</v>
-      </c>
-      <c r="G120">
-        <v>9</v>
-      </c>
-      <c r="K120">
-        <v>1998</v>
-      </c>
-    </row>
-    <row r="121" spans="1:11">
-      <c r="A121" t="s">
-        <v>0</v>
-      </c>
-      <c r="B121" t="s">
-        <v>53</v>
-      </c>
-      <c r="C121" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F121">
-        <v>7828080</v>
-      </c>
-      <c r="G121">
-        <v>10</v>
-      </c>
-      <c r="K121">
-        <v>1999</v>
-      </c>
-    </row>
-    <row r="122" spans="1:11">
-      <c r="A122" t="s">
-        <v>0</v>
-      </c>
-      <c r="B122" t="s">
-        <v>53</v>
-      </c>
-      <c r="C122" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F122">
-        <v>8075465.8560000006</v>
-      </c>
-      <c r="G122">
-        <v>11</v>
-      </c>
-      <c r="K122">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="123" spans="1:11">
-      <c r="A123" t="s">
-        <v>0</v>
-      </c>
-      <c r="B123" t="s">
-        <v>53</v>
-      </c>
-      <c r="C123" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F123">
-        <v>7655924</v>
-      </c>
-      <c r="G123">
-        <v>12</v>
-      </c>
-      <c r="K123">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="124" spans="1:11">
-      <c r="A124" t="s">
-        <v>0</v>
-      </c>
-      <c r="B124" t="s">
-        <v>53</v>
-      </c>
-      <c r="C124" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F124">
-        <v>7748178</v>
-      </c>
-      <c r="G124">
-        <v>13</v>
-      </c>
-      <c r="K124">
-        <v>2002</v>
-      </c>
-    </row>
-    <row r="125" spans="1:11">
-      <c r="A125" t="s">
-        <v>0</v>
-      </c>
-      <c r="B125" t="s">
-        <v>53</v>
-      </c>
-      <c r="C125" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F125">
-        <v>7706104</v>
-      </c>
-      <c r="G125">
-        <v>14</v>
-      </c>
-      <c r="K125">
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="126" spans="1:11">
-      <c r="A126" t="s">
-        <v>0</v>
-      </c>
-      <c r="B126" t="s">
-        <v>53</v>
-      </c>
-      <c r="C126" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F126">
-        <v>7898332</v>
-      </c>
-      <c r="G126">
-        <v>15</v>
-      </c>
-      <c r="K126">
-        <v>2004</v>
-      </c>
-    </row>
-    <row r="127" spans="1:11">
-      <c r="A127" t="s">
-        <v>0</v>
-      </c>
-      <c r="B127" t="s">
-        <v>53</v>
-      </c>
-      <c r="C127" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F127">
-        <v>7526228</v>
-      </c>
-      <c r="G127">
-        <v>16</v>
-      </c>
-      <c r="K127">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="128" spans="1:11">
-      <c r="A128" t="s">
-        <v>0</v>
-      </c>
-      <c r="B128" t="s">
-        <v>53</v>
-      </c>
-      <c r="C128" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F128">
-        <v>7020954</v>
-      </c>
-      <c r="G128">
-        <v>17</v>
-      </c>
-      <c r="K128">
-        <v>2006</v>
-      </c>
-    </row>
-    <row r="129" spans="1:11">
-      <c r="A129" t="s">
-        <v>0</v>
-      </c>
-      <c r="B129" t="s">
-        <v>53</v>
-      </c>
-      <c r="C129" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F129">
-        <v>6703662</v>
-      </c>
-      <c r="G129">
-        <v>18</v>
-      </c>
-      <c r="K129">
-        <v>2007</v>
-      </c>
-    </row>
-    <row r="130" spans="1:11">
-      <c r="A130" t="s">
-        <v>0</v>
-      </c>
-      <c r="B130" t="s">
-        <v>53</v>
-      </c>
-      <c r="C130" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F130">
-        <v>6094554</v>
-      </c>
-      <c r="G130">
-        <v>19</v>
-      </c>
-      <c r="K130">
-        <v>2008</v>
-      </c>
-    </row>
-    <row r="131" spans="1:11">
-      <c r="A131" t="s">
-        <v>0</v>
-      </c>
-      <c r="B131" t="s">
-        <v>53</v>
-      </c>
-      <c r="C131" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F131">
-        <v>4949678</v>
-      </c>
-      <c r="G131">
-        <v>20</v>
-      </c>
-      <c r="K131">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="132" spans="1:11">
-      <c r="A132" t="s">
-        <v>0</v>
-      </c>
-      <c r="B132" t="s">
-        <v>53</v>
-      </c>
-      <c r="C132" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F132">
-        <v>4923430</v>
-      </c>
-      <c r="G132">
-        <v>21</v>
-      </c>
-      <c r="K132">
-        <v>2010</v>
-      </c>
-    </row>
-    <row r="133" spans="1:11">
-      <c r="A133" t="s">
-        <v>0</v>
-      </c>
-      <c r="B133" t="s">
-        <v>53</v>
-      </c>
-      <c r="C133" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F133">
-        <v>4654002</v>
-      </c>
-      <c r="G133">
-        <v>22</v>
-      </c>
-      <c r="K133">
-        <v>2011</v>
-      </c>
-    </row>
-    <row r="134" spans="1:11">
-      <c r="A134" t="s">
-        <v>0</v>
-      </c>
-      <c r="B134" t="s">
-        <v>53</v>
-      </c>
-      <c r="C134" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F134">
-        <v>4151816</v>
-      </c>
-      <c r="G134">
-        <v>23</v>
-      </c>
-      <c r="K134">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="135" spans="1:11">
-      <c r="A135" t="s">
-        <v>0</v>
-      </c>
-      <c r="B135" t="s">
-        <v>53</v>
-      </c>
-      <c r="C135" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F135">
-        <v>4313164</v>
-      </c>
-      <c r="G135">
-        <v>24</v>
-      </c>
-      <c r="K135">
-        <v>2013</v>
-      </c>
-    </row>
-    <row r="136" spans="1:11">
-      <c r="A136" t="s">
-        <v>0</v>
-      </c>
-      <c r="B136" t="s">
-        <v>53</v>
-      </c>
-      <c r="C136" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F136">
-        <v>4159150</v>
-      </c>
-      <c r="G136">
-        <v>25</v>
-      </c>
-      <c r="K136">
-        <v>2014</v>
-      </c>
-    </row>
-    <row r="137" spans="1:11">
-      <c r="A137" t="s">
-        <v>0</v>
-      </c>
-      <c r="B137" t="s">
-        <v>53</v>
-      </c>
-      <c r="C137" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F137">
-        <v>3975800</v>
-      </c>
-      <c r="G137">
-        <v>26</v>
-      </c>
-      <c r="K137">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="138" spans="1:11">
-      <c r="A138" t="s">
-        <v>0</v>
-      </c>
-      <c r="B138" t="s">
-        <v>53</v>
-      </c>
-      <c r="C138" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F138">
-        <v>3825646</v>
-      </c>
-      <c r="G138">
-        <v>27</v>
-      </c>
-      <c r="K138">
-        <v>2016</v>
-      </c>
-    </row>
-    <row r="139" spans="1:11">
-      <c r="A139" t="s">
-        <v>0</v>
-      </c>
-      <c r="B139" t="s">
-        <v>53</v>
-      </c>
-      <c r="C139" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F139">
-        <v>3843788</v>
-      </c>
-      <c r="G139">
-        <v>28</v>
-      </c>
-      <c r="K139">
-        <v>2017</v>
-      </c>
-    </row>
-    <row r="140" spans="1:11">
-      <c r="A140" t="s">
-        <v>0</v>
-      </c>
-      <c r="B140" t="s">
-        <v>53</v>
-      </c>
-      <c r="C140" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F140">
-        <v>3914812</v>
-      </c>
-      <c r="G140">
-        <v>29</v>
-      </c>
-      <c r="K140">
-        <v>2018</v>
-      </c>
-    </row>
-    <row r="141" spans="1:11">
-      <c r="A141" t="s">
-        <v>0</v>
-      </c>
-      <c r="B141" t="s">
-        <v>53</v>
-      </c>
-      <c r="C141" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F141">
-        <v>3673948</v>
-      </c>
-      <c r="G141">
-        <v>30</v>
-      </c>
-      <c r="K141">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="142" spans="1:11">
-      <c r="A142" t="s">
-        <v>0</v>
-      </c>
-      <c r="B142" t="s">
-        <v>53</v>
-      </c>
-      <c r="C142" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F142">
-        <v>3362600.4</v>
-      </c>
-      <c r="G142">
-        <v>31</v>
-      </c>
-      <c r="K142">
-        <v>2020</v>
-      </c>
-    </row>
-    <row r="143" spans="1:11">
-      <c r="A143" t="s">
-        <v>0</v>
-      </c>
-      <c r="B143" t="s">
-        <v>53</v>
-      </c>
-      <c r="C143" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F143">
-        <v>3573742.4</v>
-      </c>
-      <c r="G143">
-        <v>32</v>
-      </c>
-      <c r="K143">
-        <v>2021</v>
-      </c>
-    </row>
-    <row r="144" spans="1:11">
-      <c r="A144" t="s">
-        <v>0</v>
-      </c>
-      <c r="B144" t="s">
-        <v>53</v>
-      </c>
-      <c r="C144" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F144">
-        <v>3497314.4</v>
-      </c>
-      <c r="G144">
-        <v>33</v>
-      </c>
-      <c r="K144">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="145" spans="1:11">
-      <c r="A145" t="s">
-        <v>0</v>
-      </c>
-      <c r="B145" t="s">
-        <v>53</v>
-      </c>
-      <c r="C145" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F145">
-        <v>3159973.1740000001</v>
-      </c>
-      <c r="G145">
-        <v>34</v>
-      </c>
-      <c r="K145">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="146" spans="1:11">
-      <c r="A146" t="s">
-        <v>0</v>
-      </c>
-      <c r="B146" t="s">
-        <v>53</v>
-      </c>
-      <c r="C146" t="str">
-        <f>'Inputs - Flow Network'!$C$6</f>
-        <v>Paper, CA</v>
-      </c>
-      <c r="F146">
-        <v>3224445.9820000003</v>
-      </c>
-      <c r="G146">
-        <v>35</v>
-      </c>
-      <c r="K146">
-        <v>2024</v>
       </c>
     </row>
   </sheetData>
@@ -5352,153 +2277,153 @@
   <sheetData>
     <row r="1" spans="2:7" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="2:7">
       <c r="B3" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="2:7">
       <c r="B4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="C7" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="9" spans="2:7" s="3" customFormat="1">
       <c r="B9" s="2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="11" spans="2:7" s="3" customFormat="1">
       <c r="B11" s="2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="2:7" s="3" customFormat="1">
       <c r="B13" s="2" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="F13" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G13" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="15" spans="2:7">
       <c r="B15" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="16" spans="2:7">
       <c r="B16" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C16" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18" spans="2:5" s="3" customFormat="1">
       <c r="B18" s="2" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D18" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="20" spans="2:5" s="3" customFormat="1">
       <c r="B20" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="2:5" s="3" customFormat="1">
       <c r="B22" s="2" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -5525,36 +2450,36 @@
   <sheetData>
     <row r="1" spans="2:8" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="2" spans="2:8">
       <c r="B2" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E2">
         <v>998</v>
@@ -5562,40 +2487,40 @@
     </row>
     <row r="5" spans="2:8" s="3" customFormat="1">
       <c r="B5" s="2" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="2:8">
       <c r="B6" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="2:8" s="3" customFormat="1">
       <c r="B8" s="2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="2:8">
       <c r="B10" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C10" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="D10" t="str">
         <f>C6</f>
@@ -5604,21 +2529,21 @@
     </row>
     <row r="13" spans="2:8" s="3" customFormat="1">
       <c r="B13" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C14" t="str">
         <f>C10</f>
@@ -5650,77 +2575,77 @@
   <sheetData>
     <row r="1" spans="2:6" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="E1" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="3" spans="2:6">
       <c r="B3" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="D3" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="2:6" s="3" customFormat="1">
       <c r="B7" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>34</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="9" spans="2:6">
       <c r="B9" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C9" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
     </row>
     <row r="12" spans="2:6" s="3" customFormat="1">
       <c r="B12" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14" spans="2:6">
       <c r="B14" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C14" t="str">
         <f>C9</f>
@@ -5731,7 +2656,7 @@
         <v>Gamma (2.07 80.2)</v>
       </c>
       <c r="E14" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="F14">
         <v>1</v>
@@ -5739,21 +2664,21 @@
     </row>
     <row r="19" spans="2:5" s="3" customFormat="1">
       <c r="B19" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>93</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C21" t="str">
         <f>$C$3</f>
@@ -5768,7 +2693,7 @@
     </row>
     <row r="22" spans="2:5">
       <c r="B22" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" ref="C22:C85" si="0">$C$3</f>
@@ -5783,7 +2708,7 @@
     </row>
     <row r="23" spans="2:5">
       <c r="B23" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="0"/>
@@ -5798,7 +2723,7 @@
     </row>
     <row r="24" spans="2:5">
       <c r="B24" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
@@ -5813,7 +2738,7 @@
     </row>
     <row r="25" spans="2:5">
       <c r="B25" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
@@ -5828,7 +2753,7 @@
     </row>
     <row r="26" spans="2:5">
       <c r="B26" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -5843,7 +2768,7 @@
     </row>
     <row r="27" spans="2:5">
       <c r="B27" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -5858,7 +2783,7 @@
     </row>
     <row r="28" spans="2:5">
       <c r="B28" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -5873,7 +2798,7 @@
     </row>
     <row r="29" spans="2:5">
       <c r="B29" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -5888,7 +2813,7 @@
     </row>
     <row r="30" spans="2:5">
       <c r="B30" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
@@ -5903,7 +2828,7 @@
     </row>
     <row r="31" spans="2:5">
       <c r="B31" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="0"/>
@@ -5918,7 +2843,7 @@
     </row>
     <row r="32" spans="2:5">
       <c r="B32" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="0"/>
@@ -5933,7 +2858,7 @@
     </row>
     <row r="33" spans="2:5">
       <c r="B33" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="0"/>
@@ -5948,7 +2873,7 @@
     </row>
     <row r="34" spans="2:5">
       <c r="B34" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="0"/>
@@ -5963,7 +2888,7 @@
     </row>
     <row r="35" spans="2:5">
       <c r="B35" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="0"/>
@@ -5978,7 +2903,7 @@
     </row>
     <row r="36" spans="2:5">
       <c r="B36" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="0"/>
@@ -5993,7 +2918,7 @@
     </row>
     <row r="37" spans="2:5">
       <c r="B37" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C37" t="str">
         <f t="shared" si="0"/>
@@ -6008,7 +2933,7 @@
     </row>
     <row r="38" spans="2:5">
       <c r="B38" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C38" t="str">
         <f t="shared" si="0"/>
@@ -6023,7 +2948,7 @@
     </row>
     <row r="39" spans="2:5">
       <c r="B39" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C39" t="str">
         <f t="shared" si="0"/>
@@ -6038,7 +2963,7 @@
     </row>
     <row r="40" spans="2:5">
       <c r="B40" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C40" t="str">
         <f t="shared" si="0"/>
@@ -6053,7 +2978,7 @@
     </row>
     <row r="41" spans="2:5">
       <c r="B41" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C41" t="str">
         <f t="shared" si="0"/>
@@ -6068,7 +2993,7 @@
     </row>
     <row r="42" spans="2:5">
       <c r="B42" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C42" t="str">
         <f t="shared" si="0"/>
@@ -6083,7 +3008,7 @@
     </row>
     <row r="43" spans="2:5">
       <c r="B43" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C43" t="str">
         <f t="shared" si="0"/>
@@ -6098,7 +3023,7 @@
     </row>
     <row r="44" spans="2:5">
       <c r="B44" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C44" t="str">
         <f t="shared" si="0"/>
@@ -6113,7 +3038,7 @@
     </row>
     <row r="45" spans="2:5">
       <c r="B45" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C45" t="str">
         <f t="shared" si="0"/>
@@ -6128,7 +3053,7 @@
     </row>
     <row r="46" spans="2:5">
       <c r="B46" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C46" t="str">
         <f t="shared" si="0"/>
@@ -6143,7 +3068,7 @@
     </row>
     <row r="47" spans="2:5">
       <c r="B47" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C47" t="str">
         <f t="shared" si="0"/>
@@ -6158,7 +3083,7 @@
     </row>
     <row r="48" spans="2:5">
       <c r="B48" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C48" t="str">
         <f t="shared" si="0"/>
@@ -6173,7 +3098,7 @@
     </row>
     <row r="49" spans="2:5">
       <c r="B49" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C49" t="str">
         <f t="shared" si="0"/>
@@ -6188,7 +3113,7 @@
     </row>
     <row r="50" spans="2:5">
       <c r="B50" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C50" t="str">
         <f t="shared" si="0"/>
@@ -6203,7 +3128,7 @@
     </row>
     <row r="51" spans="2:5">
       <c r="B51" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C51" t="str">
         <f t="shared" si="0"/>
@@ -6218,7 +3143,7 @@
     </row>
     <row r="52" spans="2:5">
       <c r="B52" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C52" t="str">
         <f t="shared" si="0"/>
@@ -6233,7 +3158,7 @@
     </row>
     <row r="53" spans="2:5">
       <c r="B53" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C53" t="str">
         <f t="shared" si="0"/>
@@ -6248,7 +3173,7 @@
     </row>
     <row r="54" spans="2:5">
       <c r="B54" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C54" t="str">
         <f t="shared" si="0"/>
@@ -6263,7 +3188,7 @@
     </row>
     <row r="55" spans="2:5">
       <c r="B55" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C55" t="str">
         <f t="shared" si="0"/>
@@ -6278,7 +3203,7 @@
     </row>
     <row r="56" spans="2:5">
       <c r="B56" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C56" t="str">
         <f t="shared" si="0"/>
@@ -6293,7 +3218,7 @@
     </row>
     <row r="57" spans="2:5">
       <c r="B57" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C57" t="str">
         <f t="shared" si="0"/>
@@ -6308,7 +3233,7 @@
     </row>
     <row r="58" spans="2:5">
       <c r="B58" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C58" t="str">
         <f t="shared" si="0"/>
@@ -6323,7 +3248,7 @@
     </row>
     <row r="59" spans="2:5">
       <c r="B59" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C59" t="str">
         <f t="shared" si="0"/>
@@ -6338,7 +3263,7 @@
     </row>
     <row r="60" spans="2:5">
       <c r="B60" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C60" t="str">
         <f t="shared" si="0"/>
@@ -6353,7 +3278,7 @@
     </row>
     <row r="61" spans="2:5">
       <c r="B61" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C61" t="str">
         <f t="shared" si="0"/>
@@ -6368,7 +3293,7 @@
     </row>
     <row r="62" spans="2:5">
       <c r="B62" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C62" t="str">
         <f t="shared" si="0"/>
@@ -6383,7 +3308,7 @@
     </row>
     <row r="63" spans="2:5">
       <c r="B63" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C63" t="str">
         <f t="shared" si="0"/>
@@ -6398,7 +3323,7 @@
     </row>
     <row r="64" spans="2:5">
       <c r="B64" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C64" t="str">
         <f t="shared" si="0"/>
@@ -6413,7 +3338,7 @@
     </row>
     <row r="65" spans="2:5">
       <c r="B65" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C65" t="str">
         <f t="shared" si="0"/>
@@ -6428,7 +3353,7 @@
     </row>
     <row r="66" spans="2:5">
       <c r="B66" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C66" t="str">
         <f t="shared" si="0"/>
@@ -6443,7 +3368,7 @@
     </row>
     <row r="67" spans="2:5">
       <c r="B67" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C67" t="str">
         <f t="shared" si="0"/>
@@ -6458,7 +3383,7 @@
     </row>
     <row r="68" spans="2:5">
       <c r="B68" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C68" t="str">
         <f t="shared" si="0"/>
@@ -6473,7 +3398,7 @@
     </row>
     <row r="69" spans="2:5">
       <c r="B69" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C69" t="str">
         <f t="shared" si="0"/>
@@ -6488,7 +3413,7 @@
     </row>
     <row r="70" spans="2:5">
       <c r="B70" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C70" t="str">
         <f t="shared" si="0"/>
@@ -6503,7 +3428,7 @@
     </row>
     <row r="71" spans="2:5">
       <c r="B71" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C71" t="str">
         <f t="shared" si="0"/>
@@ -6518,7 +3443,7 @@
     </row>
     <row r="72" spans="2:5">
       <c r="B72" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C72" t="str">
         <f t="shared" si="0"/>
@@ -6533,7 +3458,7 @@
     </row>
     <row r="73" spans="2:5">
       <c r="B73" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C73" t="str">
         <f t="shared" si="0"/>
@@ -6548,7 +3473,7 @@
     </row>
     <row r="74" spans="2:5">
       <c r="B74" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C74" t="str">
         <f t="shared" si="0"/>
@@ -6563,7 +3488,7 @@
     </row>
     <row r="75" spans="2:5">
       <c r="B75" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C75" t="str">
         <f t="shared" si="0"/>
@@ -6578,7 +3503,7 @@
     </row>
     <row r="76" spans="2:5">
       <c r="B76" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C76" t="str">
         <f t="shared" si="0"/>
@@ -6593,7 +3518,7 @@
     </row>
     <row r="77" spans="2:5">
       <c r="B77" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C77" t="str">
         <f t="shared" si="0"/>
@@ -6608,7 +3533,7 @@
     </row>
     <row r="78" spans="2:5">
       <c r="B78" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C78" t="str">
         <f t="shared" si="0"/>
@@ -6623,7 +3548,7 @@
     </row>
     <row r="79" spans="2:5">
       <c r="B79" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C79" t="str">
         <f t="shared" si="0"/>
@@ -6638,7 +3563,7 @@
     </row>
     <row r="80" spans="2:5">
       <c r="B80" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C80" t="str">
         <f t="shared" si="0"/>
@@ -6653,7 +3578,7 @@
     </row>
     <row r="81" spans="2:5">
       <c r="B81" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C81" t="str">
         <f t="shared" si="0"/>
@@ -6668,7 +3593,7 @@
     </row>
     <row r="82" spans="2:5">
       <c r="B82" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C82" t="str">
         <f t="shared" si="0"/>
@@ -6683,7 +3608,7 @@
     </row>
     <row r="83" spans="2:5">
       <c r="B83" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C83" t="str">
         <f t="shared" si="0"/>
@@ -6698,7 +3623,7 @@
     </row>
     <row r="84" spans="2:5">
       <c r="B84" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C84" t="str">
         <f t="shared" si="0"/>
@@ -6713,7 +3638,7 @@
     </row>
     <row r="85" spans="2:5">
       <c r="B85" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C85" t="str">
         <f t="shared" si="0"/>
@@ -6728,7 +3653,7 @@
     </row>
     <row r="86" spans="2:5">
       <c r="B86" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C86" t="str">
         <f t="shared" ref="C86:C149" si="1">$C$3</f>
@@ -6743,7 +3668,7 @@
     </row>
     <row r="87" spans="2:5">
       <c r="B87" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C87" t="str">
         <f t="shared" si="1"/>
@@ -6758,7 +3683,7 @@
     </row>
     <row r="88" spans="2:5">
       <c r="B88" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C88" t="str">
         <f t="shared" si="1"/>
@@ -6773,7 +3698,7 @@
     </row>
     <row r="89" spans="2:5">
       <c r="B89" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C89" t="str">
         <f t="shared" si="1"/>
@@ -6788,7 +3713,7 @@
     </row>
     <row r="90" spans="2:5">
       <c r="B90" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C90" t="str">
         <f t="shared" si="1"/>
@@ -6803,7 +3728,7 @@
     </row>
     <row r="91" spans="2:5">
       <c r="B91" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C91" t="str">
         <f t="shared" si="1"/>
@@ -6818,7 +3743,7 @@
     </row>
     <row r="92" spans="2:5">
       <c r="B92" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C92" t="str">
         <f t="shared" si="1"/>
@@ -6833,7 +3758,7 @@
     </row>
     <row r="93" spans="2:5">
       <c r="B93" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C93" t="str">
         <f t="shared" si="1"/>
@@ -6848,7 +3773,7 @@
     </row>
     <row r="94" spans="2:5">
       <c r="B94" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C94" t="str">
         <f t="shared" si="1"/>
@@ -6863,7 +3788,7 @@
     </row>
     <row r="95" spans="2:5">
       <c r="B95" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C95" t="str">
         <f t="shared" si="1"/>
@@ -6878,7 +3803,7 @@
     </row>
     <row r="96" spans="2:5">
       <c r="B96" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C96" t="str">
         <f t="shared" si="1"/>
@@ -6893,7 +3818,7 @@
     </row>
     <row r="97" spans="2:5">
       <c r="B97" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C97" t="str">
         <f t="shared" si="1"/>
@@ -6908,7 +3833,7 @@
     </row>
     <row r="98" spans="2:5">
       <c r="B98" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C98" t="str">
         <f t="shared" si="1"/>
@@ -6923,7 +3848,7 @@
     </row>
     <row r="99" spans="2:5">
       <c r="B99" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C99" t="str">
         <f t="shared" si="1"/>
@@ -6938,7 +3863,7 @@
     </row>
     <row r="100" spans="2:5">
       <c r="B100" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C100" t="str">
         <f t="shared" si="1"/>
@@ -6953,7 +3878,7 @@
     </row>
     <row r="101" spans="2:5">
       <c r="B101" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C101" t="str">
         <f t="shared" si="1"/>
@@ -6968,7 +3893,7 @@
     </row>
     <row r="102" spans="2:5">
       <c r="B102" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C102" t="str">
         <f t="shared" si="1"/>
@@ -6983,7 +3908,7 @@
     </row>
     <row r="103" spans="2:5">
       <c r="B103" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C103" t="str">
         <f t="shared" si="1"/>
@@ -6998,7 +3923,7 @@
     </row>
     <row r="104" spans="2:5">
       <c r="B104" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C104" t="str">
         <f t="shared" si="1"/>
@@ -7013,7 +3938,7 @@
     </row>
     <row r="105" spans="2:5">
       <c r="B105" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C105" t="str">
         <f t="shared" si="1"/>
@@ -7028,7 +3953,7 @@
     </row>
     <row r="106" spans="2:5">
       <c r="B106" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C106" t="str">
         <f t="shared" si="1"/>
@@ -7043,7 +3968,7 @@
     </row>
     <row r="107" spans="2:5">
       <c r="B107" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C107" t="str">
         <f t="shared" si="1"/>
@@ -7058,7 +3983,7 @@
     </row>
     <row r="108" spans="2:5">
       <c r="B108" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C108" t="str">
         <f t="shared" si="1"/>
@@ -7073,7 +3998,7 @@
     </row>
     <row r="109" spans="2:5">
       <c r="B109" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C109" t="str">
         <f t="shared" si="1"/>
@@ -7088,7 +4013,7 @@
     </row>
     <row r="110" spans="2:5">
       <c r="B110" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C110" t="str">
         <f t="shared" si="1"/>
@@ -7103,7 +4028,7 @@
     </row>
     <row r="111" spans="2:5">
       <c r="B111" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C111" t="str">
         <f t="shared" si="1"/>
@@ -7118,7 +4043,7 @@
     </row>
     <row r="112" spans="2:5">
       <c r="B112" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C112" t="str">
         <f t="shared" si="1"/>
@@ -7133,7 +4058,7 @@
     </row>
     <row r="113" spans="2:5">
       <c r="B113" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C113" t="str">
         <f t="shared" si="1"/>
@@ -7148,7 +4073,7 @@
     </row>
     <row r="114" spans="2:5">
       <c r="B114" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C114" t="str">
         <f t="shared" si="1"/>
@@ -7163,7 +4088,7 @@
     </row>
     <row r="115" spans="2:5">
       <c r="B115" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C115" t="str">
         <f t="shared" si="1"/>
@@ -7178,7 +4103,7 @@
     </row>
     <row r="116" spans="2:5">
       <c r="B116" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C116" t="str">
         <f t="shared" si="1"/>
@@ -7193,7 +4118,7 @@
     </row>
     <row r="117" spans="2:5">
       <c r="B117" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C117" t="str">
         <f t="shared" si="1"/>
@@ -7208,7 +4133,7 @@
     </row>
     <row r="118" spans="2:5">
       <c r="B118" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C118" t="str">
         <f t="shared" si="1"/>
@@ -7223,7 +4148,7 @@
     </row>
     <row r="119" spans="2:5">
       <c r="B119" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C119" t="str">
         <f t="shared" si="1"/>
@@ -7238,7 +4163,7 @@
     </row>
     <row r="120" spans="2:5">
       <c r="B120" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C120" t="str">
         <f t="shared" si="1"/>
@@ -7253,7 +4178,7 @@
     </row>
     <row r="121" spans="2:5">
       <c r="B121" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C121" t="str">
         <f t="shared" si="1"/>
@@ -7268,7 +4193,7 @@
     </row>
     <row r="122" spans="2:5">
       <c r="B122" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C122" t="str">
         <f t="shared" si="1"/>
@@ -7283,7 +4208,7 @@
     </row>
     <row r="123" spans="2:5">
       <c r="B123" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C123" t="str">
         <f t="shared" si="1"/>
@@ -7298,7 +4223,7 @@
     </row>
     <row r="124" spans="2:5">
       <c r="B124" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C124" t="str">
         <f t="shared" si="1"/>
@@ -7313,7 +4238,7 @@
     </row>
     <row r="125" spans="2:5">
       <c r="B125" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C125" t="str">
         <f t="shared" si="1"/>
@@ -7328,7 +4253,7 @@
     </row>
     <row r="126" spans="2:5">
       <c r="B126" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C126" t="str">
         <f t="shared" si="1"/>
@@ -7343,7 +4268,7 @@
     </row>
     <row r="127" spans="2:5">
       <c r="B127" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C127" t="str">
         <f t="shared" si="1"/>
@@ -7358,7 +4283,7 @@
     </row>
     <row r="128" spans="2:5">
       <c r="B128" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C128" t="str">
         <f t="shared" si="1"/>
@@ -7373,7 +4298,7 @@
     </row>
     <row r="129" spans="2:5">
       <c r="B129" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C129" t="str">
         <f t="shared" si="1"/>
@@ -7388,7 +4313,7 @@
     </row>
     <row r="130" spans="2:5">
       <c r="B130" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C130" t="str">
         <f t="shared" si="1"/>
@@ -7403,7 +4328,7 @@
     </row>
     <row r="131" spans="2:5">
       <c r="B131" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C131" t="str">
         <f t="shared" si="1"/>
@@ -7418,7 +4343,7 @@
     </row>
     <row r="132" spans="2:5">
       <c r="B132" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C132" t="str">
         <f t="shared" si="1"/>
@@ -7433,7 +4358,7 @@
     </row>
     <row r="133" spans="2:5">
       <c r="B133" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C133" t="str">
         <f t="shared" si="1"/>
@@ -7448,7 +4373,7 @@
     </row>
     <row r="134" spans="2:5">
       <c r="B134" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C134" t="str">
         <f t="shared" si="1"/>
@@ -7463,7 +4388,7 @@
     </row>
     <row r="135" spans="2:5">
       <c r="B135" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C135" t="str">
         <f t="shared" si="1"/>
@@ -7478,7 +4403,7 @@
     </row>
     <row r="136" spans="2:5">
       <c r="B136" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C136" t="str">
         <f t="shared" si="1"/>
@@ -7493,7 +4418,7 @@
     </row>
     <row r="137" spans="2:5">
       <c r="B137" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C137" t="str">
         <f t="shared" si="1"/>
@@ -7508,7 +4433,7 @@
     </row>
     <row r="138" spans="2:5">
       <c r="B138" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C138" t="str">
         <f t="shared" si="1"/>
@@ -7523,7 +4448,7 @@
     </row>
     <row r="139" spans="2:5">
       <c r="B139" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C139" t="str">
         <f t="shared" si="1"/>
@@ -7538,7 +4463,7 @@
     </row>
     <row r="140" spans="2:5">
       <c r="B140" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C140" t="str">
         <f t="shared" si="1"/>
@@ -7553,7 +4478,7 @@
     </row>
     <row r="141" spans="2:5">
       <c r="B141" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C141" t="str">
         <f t="shared" si="1"/>
@@ -7568,7 +4493,7 @@
     </row>
     <row r="142" spans="2:5">
       <c r="B142" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C142" t="str">
         <f t="shared" si="1"/>
@@ -7583,7 +4508,7 @@
     </row>
     <row r="143" spans="2:5">
       <c r="B143" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C143" t="str">
         <f t="shared" si="1"/>
@@ -7598,7 +4523,7 @@
     </row>
     <row r="144" spans="2:5">
       <c r="B144" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C144" t="str">
         <f t="shared" si="1"/>
@@ -7613,7 +4538,7 @@
     </row>
     <row r="145" spans="2:5">
       <c r="B145" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C145" t="str">
         <f t="shared" si="1"/>
@@ -7628,7 +4553,7 @@
     </row>
     <row r="146" spans="2:5">
       <c r="B146" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C146" t="str">
         <f t="shared" si="1"/>
@@ -7643,7 +4568,7 @@
     </row>
     <row r="147" spans="2:5">
       <c r="B147" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C147" t="str">
         <f t="shared" si="1"/>
@@ -7658,7 +4583,7 @@
     </row>
     <row r="148" spans="2:5">
       <c r="B148" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C148" t="str">
         <f t="shared" si="1"/>
@@ -7673,7 +4598,7 @@
     </row>
     <row r="149" spans="2:5">
       <c r="B149" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C149" t="str">
         <f t="shared" si="1"/>
@@ -7688,7 +4613,7 @@
     </row>
     <row r="150" spans="2:5">
       <c r="B150" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C150" t="str">
         <f t="shared" ref="C150:C213" si="2">$C$3</f>
@@ -7703,7 +4628,7 @@
     </row>
     <row r="151" spans="2:5">
       <c r="B151" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C151" t="str">
         <f t="shared" si="2"/>
@@ -7718,7 +4643,7 @@
     </row>
     <row r="152" spans="2:5">
       <c r="B152" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C152" t="str">
         <f t="shared" si="2"/>
@@ -7733,7 +4658,7 @@
     </row>
     <row r="153" spans="2:5">
       <c r="B153" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C153" t="str">
         <f t="shared" si="2"/>
@@ -7748,7 +4673,7 @@
     </row>
     <row r="154" spans="2:5">
       <c r="B154" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C154" t="str">
         <f t="shared" si="2"/>
@@ -7763,7 +4688,7 @@
     </row>
     <row r="155" spans="2:5">
       <c r="B155" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C155" t="str">
         <f t="shared" si="2"/>
@@ -7778,7 +4703,7 @@
     </row>
     <row r="156" spans="2:5">
       <c r="B156" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C156" t="str">
         <f t="shared" si="2"/>
@@ -7793,7 +4718,7 @@
     </row>
     <row r="157" spans="2:5">
       <c r="B157" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C157" t="str">
         <f t="shared" si="2"/>
@@ -7808,7 +4733,7 @@
     </row>
     <row r="158" spans="2:5">
       <c r="B158" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C158" t="str">
         <f t="shared" si="2"/>
@@ -7823,7 +4748,7 @@
     </row>
     <row r="159" spans="2:5">
       <c r="B159" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C159" t="str">
         <f t="shared" si="2"/>
@@ -7838,7 +4763,7 @@
     </row>
     <row r="160" spans="2:5">
       <c r="B160" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C160" t="str">
         <f t="shared" si="2"/>
@@ -7853,7 +4778,7 @@
     </row>
     <row r="161" spans="2:5">
       <c r="B161" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C161" t="str">
         <f t="shared" si="2"/>
@@ -7868,7 +4793,7 @@
     </row>
     <row r="162" spans="2:5">
       <c r="B162" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C162" t="str">
         <f t="shared" si="2"/>
@@ -7883,7 +4808,7 @@
     </row>
     <row r="163" spans="2:5">
       <c r="B163" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C163" t="str">
         <f t="shared" si="2"/>
@@ -7898,7 +4823,7 @@
     </row>
     <row r="164" spans="2:5">
       <c r="B164" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C164" t="str">
         <f t="shared" si="2"/>
@@ -7913,7 +4838,7 @@
     </row>
     <row r="165" spans="2:5">
       <c r="B165" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C165" t="str">
         <f t="shared" si="2"/>
@@ -7928,7 +4853,7 @@
     </row>
     <row r="166" spans="2:5">
       <c r="B166" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C166" t="str">
         <f t="shared" si="2"/>
@@ -7943,7 +4868,7 @@
     </row>
     <row r="167" spans="2:5">
       <c r="B167" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C167" t="str">
         <f t="shared" si="2"/>
@@ -7958,7 +4883,7 @@
     </row>
     <row r="168" spans="2:5">
       <c r="B168" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C168" t="str">
         <f t="shared" si="2"/>
@@ -7973,7 +4898,7 @@
     </row>
     <row r="169" spans="2:5">
       <c r="B169" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C169" t="str">
         <f t="shared" si="2"/>
@@ -7988,7 +4913,7 @@
     </row>
     <row r="170" spans="2:5">
       <c r="B170" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C170" t="str">
         <f t="shared" si="2"/>
@@ -8003,7 +4928,7 @@
     </row>
     <row r="171" spans="2:5">
       <c r="B171" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C171" t="str">
         <f t="shared" si="2"/>
@@ -8018,7 +4943,7 @@
     </row>
     <row r="172" spans="2:5">
       <c r="B172" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C172" t="str">
         <f t="shared" si="2"/>
@@ -8033,7 +4958,7 @@
     </row>
     <row r="173" spans="2:5">
       <c r="B173" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C173" t="str">
         <f t="shared" si="2"/>
@@ -8048,7 +4973,7 @@
     </row>
     <row r="174" spans="2:5">
       <c r="B174" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C174" t="str">
         <f t="shared" si="2"/>
@@ -8063,7 +4988,7 @@
     </row>
     <row r="175" spans="2:5">
       <c r="B175" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C175" t="str">
         <f t="shared" si="2"/>
@@ -8078,7 +5003,7 @@
     </row>
     <row r="176" spans="2:5">
       <c r="B176" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C176" t="str">
         <f t="shared" si="2"/>
@@ -8093,7 +5018,7 @@
     </row>
     <row r="177" spans="2:5">
       <c r="B177" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C177" t="str">
         <f t="shared" si="2"/>
@@ -8108,7 +5033,7 @@
     </row>
     <row r="178" spans="2:5">
       <c r="B178" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C178" t="str">
         <f t="shared" si="2"/>
@@ -8123,7 +5048,7 @@
     </row>
     <row r="179" spans="2:5">
       <c r="B179" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C179" t="str">
         <f t="shared" si="2"/>
@@ -8138,7 +5063,7 @@
     </row>
     <row r="180" spans="2:5">
       <c r="B180" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C180" t="str">
         <f t="shared" si="2"/>
@@ -8153,7 +5078,7 @@
     </row>
     <row r="181" spans="2:5">
       <c r="B181" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C181" t="str">
         <f t="shared" si="2"/>
@@ -8168,7 +5093,7 @@
     </row>
     <row r="182" spans="2:5">
       <c r="B182" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C182" t="str">
         <f t="shared" si="2"/>
@@ -8183,7 +5108,7 @@
     </row>
     <row r="183" spans="2:5">
       <c r="B183" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C183" t="str">
         <f t="shared" si="2"/>
@@ -8198,7 +5123,7 @@
     </row>
     <row r="184" spans="2:5">
       <c r="B184" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C184" t="str">
         <f t="shared" si="2"/>
@@ -8213,7 +5138,7 @@
     </row>
     <row r="185" spans="2:5">
       <c r="B185" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C185" t="str">
         <f t="shared" si="2"/>
@@ -8228,7 +5153,7 @@
     </row>
     <row r="186" spans="2:5">
       <c r="B186" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C186" t="str">
         <f t="shared" si="2"/>
@@ -8243,7 +5168,7 @@
     </row>
     <row r="187" spans="2:5">
       <c r="B187" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C187" t="str">
         <f t="shared" si="2"/>
@@ -8258,7 +5183,7 @@
     </row>
     <row r="188" spans="2:5">
       <c r="B188" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C188" t="str">
         <f t="shared" si="2"/>
@@ -8273,7 +5198,7 @@
     </row>
     <row r="189" spans="2:5">
       <c r="B189" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C189" t="str">
         <f t="shared" si="2"/>
@@ -8288,7 +5213,7 @@
     </row>
     <row r="190" spans="2:5">
       <c r="B190" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C190" t="str">
         <f t="shared" si="2"/>
@@ -8303,7 +5228,7 @@
     </row>
     <row r="191" spans="2:5">
       <c r="B191" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C191" t="str">
         <f t="shared" si="2"/>
@@ -8318,7 +5243,7 @@
     </row>
     <row r="192" spans="2:5">
       <c r="B192" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C192" t="str">
         <f t="shared" si="2"/>
@@ -8333,7 +5258,7 @@
     </row>
     <row r="193" spans="2:5">
       <c r="B193" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C193" t="str">
         <f t="shared" si="2"/>
@@ -8348,7 +5273,7 @@
     </row>
     <row r="194" spans="2:5">
       <c r="B194" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C194" t="str">
         <f t="shared" si="2"/>
@@ -8363,7 +5288,7 @@
     </row>
     <row r="195" spans="2:5">
       <c r="B195" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C195" t="str">
         <f t="shared" si="2"/>
@@ -8378,7 +5303,7 @@
     </row>
     <row r="196" spans="2:5">
       <c r="B196" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C196" t="str">
         <f t="shared" si="2"/>
@@ -8393,7 +5318,7 @@
     </row>
     <row r="197" spans="2:5">
       <c r="B197" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C197" t="str">
         <f t="shared" si="2"/>
@@ -8408,7 +5333,7 @@
     </row>
     <row r="198" spans="2:5">
       <c r="B198" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C198" t="str">
         <f t="shared" si="2"/>
@@ -8423,7 +5348,7 @@
     </row>
     <row r="199" spans="2:5">
       <c r="B199" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C199" t="str">
         <f t="shared" si="2"/>
@@ -8438,7 +5363,7 @@
     </row>
     <row r="200" spans="2:5">
       <c r="B200" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C200" t="str">
         <f t="shared" si="2"/>
@@ -8453,7 +5378,7 @@
     </row>
     <row r="201" spans="2:5">
       <c r="B201" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C201" t="str">
         <f t="shared" si="2"/>
@@ -8468,7 +5393,7 @@
     </row>
     <row r="202" spans="2:5">
       <c r="B202" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C202" t="str">
         <f t="shared" si="2"/>
@@ -8483,7 +5408,7 @@
     </row>
     <row r="203" spans="2:5">
       <c r="B203" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C203" t="str">
         <f t="shared" si="2"/>
@@ -8498,7 +5423,7 @@
     </row>
     <row r="204" spans="2:5">
       <c r="B204" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C204" t="str">
         <f t="shared" si="2"/>
@@ -8513,7 +5438,7 @@
     </row>
     <row r="205" spans="2:5">
       <c r="B205" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C205" t="str">
         <f t="shared" si="2"/>
@@ -8528,7 +5453,7 @@
     </row>
     <row r="206" spans="2:5">
       <c r="B206" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C206" t="str">
         <f t="shared" si="2"/>
@@ -8543,7 +5468,7 @@
     </row>
     <row r="207" spans="2:5">
       <c r="B207" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C207" t="str">
         <f t="shared" si="2"/>
@@ -8558,7 +5483,7 @@
     </row>
     <row r="208" spans="2:5">
       <c r="B208" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C208" t="str">
         <f t="shared" si="2"/>
@@ -8573,7 +5498,7 @@
     </row>
     <row r="209" spans="2:5">
       <c r="B209" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C209" t="str">
         <f t="shared" si="2"/>
@@ -8588,7 +5513,7 @@
     </row>
     <row r="210" spans="2:5">
       <c r="B210" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C210" t="str">
         <f t="shared" si="2"/>
@@ -8603,7 +5528,7 @@
     </row>
     <row r="211" spans="2:5">
       <c r="B211" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C211" t="str">
         <f t="shared" si="2"/>
@@ -8618,7 +5543,7 @@
     </row>
     <row r="212" spans="2:5">
       <c r="B212" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C212" t="str">
         <f t="shared" si="2"/>
@@ -8633,7 +5558,7 @@
     </row>
     <row r="213" spans="2:5">
       <c r="B213" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C213" t="str">
         <f t="shared" si="2"/>
@@ -8648,7 +5573,7 @@
     </row>
     <row r="214" spans="2:5">
       <c r="B214" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C214" t="str">
         <f t="shared" ref="C214:C277" si="3">$C$3</f>
@@ -8663,7 +5588,7 @@
     </row>
     <row r="215" spans="2:5">
       <c r="B215" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C215" t="str">
         <f t="shared" si="3"/>
@@ -8678,7 +5603,7 @@
     </row>
     <row r="216" spans="2:5">
       <c r="B216" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C216" t="str">
         <f t="shared" si="3"/>
@@ -8693,7 +5618,7 @@
     </row>
     <row r="217" spans="2:5">
       <c r="B217" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C217" t="str">
         <f t="shared" si="3"/>
@@ -8708,7 +5633,7 @@
     </row>
     <row r="218" spans="2:5">
       <c r="B218" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C218" t="str">
         <f t="shared" si="3"/>
@@ -8723,7 +5648,7 @@
     </row>
     <row r="219" spans="2:5">
       <c r="B219" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C219" t="str">
         <f t="shared" si="3"/>
@@ -8738,7 +5663,7 @@
     </row>
     <row r="220" spans="2:5">
       <c r="B220" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C220" t="str">
         <f t="shared" si="3"/>
@@ -8753,7 +5678,7 @@
     </row>
     <row r="221" spans="2:5">
       <c r="B221" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C221" t="str">
         <f t="shared" si="3"/>
@@ -8768,7 +5693,7 @@
     </row>
     <row r="222" spans="2:5">
       <c r="B222" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C222" t="str">
         <f t="shared" si="3"/>
@@ -8783,7 +5708,7 @@
     </row>
     <row r="223" spans="2:5">
       <c r="B223" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C223" t="str">
         <f t="shared" si="3"/>
@@ -8798,7 +5723,7 @@
     </row>
     <row r="224" spans="2:5">
       <c r="B224" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C224" t="str">
         <f t="shared" si="3"/>
@@ -8813,7 +5738,7 @@
     </row>
     <row r="225" spans="2:5">
       <c r="B225" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C225" t="str">
         <f t="shared" si="3"/>
@@ -8828,7 +5753,7 @@
     </row>
     <row r="226" spans="2:5">
       <c r="B226" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C226" t="str">
         <f t="shared" si="3"/>
@@ -8843,7 +5768,7 @@
     </row>
     <row r="227" spans="2:5">
       <c r="B227" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C227" t="str">
         <f t="shared" si="3"/>
@@ -8858,7 +5783,7 @@
     </row>
     <row r="228" spans="2:5">
       <c r="B228" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C228" t="str">
         <f t="shared" si="3"/>
@@ -8873,7 +5798,7 @@
     </row>
     <row r="229" spans="2:5">
       <c r="B229" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C229" t="str">
         <f t="shared" si="3"/>
@@ -8888,7 +5813,7 @@
     </row>
     <row r="230" spans="2:5">
       <c r="B230" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C230" t="str">
         <f t="shared" si="3"/>
@@ -8903,7 +5828,7 @@
     </row>
     <row r="231" spans="2:5">
       <c r="B231" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C231" t="str">
         <f t="shared" si="3"/>
@@ -8918,7 +5843,7 @@
     </row>
     <row r="232" spans="2:5">
       <c r="B232" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C232" t="str">
         <f t="shared" si="3"/>
@@ -8933,7 +5858,7 @@
     </row>
     <row r="233" spans="2:5">
       <c r="B233" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C233" t="str">
         <f t="shared" si="3"/>
@@ -8948,7 +5873,7 @@
     </row>
     <row r="234" spans="2:5">
       <c r="B234" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C234" t="str">
         <f t="shared" si="3"/>
@@ -8963,7 +5888,7 @@
     </row>
     <row r="235" spans="2:5">
       <c r="B235" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C235" t="str">
         <f t="shared" si="3"/>
@@ -8978,7 +5903,7 @@
     </row>
     <row r="236" spans="2:5">
       <c r="B236" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C236" t="str">
         <f t="shared" si="3"/>
@@ -8993,7 +5918,7 @@
     </row>
     <row r="237" spans="2:5">
       <c r="B237" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C237" t="str">
         <f t="shared" si="3"/>
@@ -9008,7 +5933,7 @@
     </row>
     <row r="238" spans="2:5">
       <c r="B238" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C238" t="str">
         <f t="shared" si="3"/>
@@ -9023,7 +5948,7 @@
     </row>
     <row r="239" spans="2:5">
       <c r="B239" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C239" t="str">
         <f t="shared" si="3"/>
@@ -9038,7 +5963,7 @@
     </row>
     <row r="240" spans="2:5">
       <c r="B240" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C240" t="str">
         <f t="shared" si="3"/>
@@ -9053,7 +5978,7 @@
     </row>
     <row r="241" spans="2:5">
       <c r="B241" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C241" t="str">
         <f t="shared" si="3"/>
@@ -9068,7 +5993,7 @@
     </row>
     <row r="242" spans="2:5">
       <c r="B242" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C242" t="str">
         <f t="shared" si="3"/>
@@ -9083,7 +6008,7 @@
     </row>
     <row r="243" spans="2:5">
       <c r="B243" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C243" t="str">
         <f t="shared" si="3"/>
@@ -9098,7 +6023,7 @@
     </row>
     <row r="244" spans="2:5">
       <c r="B244" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C244" t="str">
         <f t="shared" si="3"/>
@@ -9113,7 +6038,7 @@
     </row>
     <row r="245" spans="2:5">
       <c r="B245" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C245" t="str">
         <f t="shared" si="3"/>
@@ -9128,7 +6053,7 @@
     </row>
     <row r="246" spans="2:5">
       <c r="B246" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C246" t="str">
         <f t="shared" si="3"/>
@@ -9143,7 +6068,7 @@
     </row>
     <row r="247" spans="2:5">
       <c r="B247" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C247" t="str">
         <f t="shared" si="3"/>
@@ -9158,7 +6083,7 @@
     </row>
     <row r="248" spans="2:5">
       <c r="B248" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C248" t="str">
         <f t="shared" si="3"/>
@@ -9173,7 +6098,7 @@
     </row>
     <row r="249" spans="2:5">
       <c r="B249" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C249" t="str">
         <f t="shared" si="3"/>
@@ -9188,7 +6113,7 @@
     </row>
     <row r="250" spans="2:5">
       <c r="B250" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C250" t="str">
         <f t="shared" si="3"/>
@@ -9203,7 +6128,7 @@
     </row>
     <row r="251" spans="2:5">
       <c r="B251" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C251" t="str">
         <f t="shared" si="3"/>
@@ -9218,7 +6143,7 @@
     </row>
     <row r="252" spans="2:5">
       <c r="B252" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C252" t="str">
         <f t="shared" si="3"/>
@@ -9233,7 +6158,7 @@
     </row>
     <row r="253" spans="2:5">
       <c r="B253" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C253" t="str">
         <f t="shared" si="3"/>
@@ -9248,7 +6173,7 @@
     </row>
     <row r="254" spans="2:5">
       <c r="B254" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C254" t="str">
         <f t="shared" si="3"/>
@@ -9263,7 +6188,7 @@
     </row>
     <row r="255" spans="2:5">
       <c r="B255" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C255" t="str">
         <f t="shared" si="3"/>
@@ -9278,7 +6203,7 @@
     </row>
     <row r="256" spans="2:5">
       <c r="B256" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C256" t="str">
         <f t="shared" si="3"/>
@@ -9293,7 +6218,7 @@
     </row>
     <row r="257" spans="2:5">
       <c r="B257" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C257" t="str">
         <f t="shared" si="3"/>
@@ -9308,7 +6233,7 @@
     </row>
     <row r="258" spans="2:5">
       <c r="B258" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C258" t="str">
         <f t="shared" si="3"/>
@@ -9323,7 +6248,7 @@
     </row>
     <row r="259" spans="2:5">
       <c r="B259" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C259" t="str">
         <f t="shared" si="3"/>
@@ -9338,7 +6263,7 @@
     </row>
     <row r="260" spans="2:5">
       <c r="B260" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C260" t="str">
         <f t="shared" si="3"/>
@@ -9353,7 +6278,7 @@
     </row>
     <row r="261" spans="2:5">
       <c r="B261" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C261" t="str">
         <f t="shared" si="3"/>
@@ -9368,7 +6293,7 @@
     </row>
     <row r="262" spans="2:5">
       <c r="B262" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C262" t="str">
         <f t="shared" si="3"/>
@@ -9383,7 +6308,7 @@
     </row>
     <row r="263" spans="2:5">
       <c r="B263" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C263" t="str">
         <f t="shared" si="3"/>
@@ -9398,7 +6323,7 @@
     </row>
     <row r="264" spans="2:5">
       <c r="B264" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C264" t="str">
         <f t="shared" si="3"/>
@@ -9413,7 +6338,7 @@
     </row>
     <row r="265" spans="2:5">
       <c r="B265" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C265" t="str">
         <f t="shared" si="3"/>
@@ -9428,7 +6353,7 @@
     </row>
     <row r="266" spans="2:5">
       <c r="B266" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C266" t="str">
         <f t="shared" si="3"/>
@@ -9443,7 +6368,7 @@
     </row>
     <row r="267" spans="2:5">
       <c r="B267" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C267" t="str">
         <f t="shared" si="3"/>
@@ -9458,7 +6383,7 @@
     </row>
     <row r="268" spans="2:5">
       <c r="B268" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C268" t="str">
         <f t="shared" si="3"/>
@@ -9473,7 +6398,7 @@
     </row>
     <row r="269" spans="2:5">
       <c r="B269" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C269" t="str">
         <f t="shared" si="3"/>
@@ -9488,7 +6413,7 @@
     </row>
     <row r="270" spans="2:5">
       <c r="B270" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C270" t="str">
         <f t="shared" si="3"/>
@@ -9503,7 +6428,7 @@
     </row>
     <row r="271" spans="2:5">
       <c r="B271" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C271" t="str">
         <f t="shared" si="3"/>
@@ -9518,7 +6443,7 @@
     </row>
     <row r="272" spans="2:5">
       <c r="B272" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C272" t="str">
         <f t="shared" si="3"/>
@@ -9533,7 +6458,7 @@
     </row>
     <row r="273" spans="2:5">
       <c r="B273" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C273" t="str">
         <f t="shared" si="3"/>
@@ -9548,7 +6473,7 @@
     </row>
     <row r="274" spans="2:5">
       <c r="B274" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C274" t="str">
         <f t="shared" si="3"/>
@@ -9563,7 +6488,7 @@
     </row>
     <row r="275" spans="2:5">
       <c r="B275" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C275" t="str">
         <f t="shared" si="3"/>
@@ -9578,7 +6503,7 @@
     </row>
     <row r="276" spans="2:5">
       <c r="B276" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C276" t="str">
         <f t="shared" si="3"/>
@@ -9593,7 +6518,7 @@
     </row>
     <row r="277" spans="2:5">
       <c r="B277" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C277" t="str">
         <f t="shared" si="3"/>
@@ -9608,7 +6533,7 @@
     </row>
     <row r="278" spans="2:5">
       <c r="B278" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C278" t="str">
         <f t="shared" ref="C278:C321" si="4">$C$3</f>
@@ -9623,7 +6548,7 @@
     </row>
     <row r="279" spans="2:5">
       <c r="B279" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C279" t="str">
         <f t="shared" si="4"/>
@@ -9638,7 +6563,7 @@
     </row>
     <row r="280" spans="2:5">
       <c r="B280" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C280" t="str">
         <f t="shared" si="4"/>
@@ -9653,7 +6578,7 @@
     </row>
     <row r="281" spans="2:5">
       <c r="B281" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C281" t="str">
         <f t="shared" si="4"/>
@@ -9668,7 +6593,7 @@
     </row>
     <row r="282" spans="2:5">
       <c r="B282" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C282" t="str">
         <f t="shared" si="4"/>
@@ -9683,7 +6608,7 @@
     </row>
     <row r="283" spans="2:5">
       <c r="B283" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C283" t="str">
         <f t="shared" si="4"/>
@@ -9698,7 +6623,7 @@
     </row>
     <row r="284" spans="2:5">
       <c r="B284" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C284" t="str">
         <f t="shared" si="4"/>
@@ -9713,7 +6638,7 @@
     </row>
     <row r="285" spans="2:5">
       <c r="B285" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C285" t="str">
         <f t="shared" si="4"/>
@@ -9728,7 +6653,7 @@
     </row>
     <row r="286" spans="2:5">
       <c r="B286" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C286" t="str">
         <f t="shared" si="4"/>
@@ -9743,7 +6668,7 @@
     </row>
     <row r="287" spans="2:5">
       <c r="B287" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C287" t="str">
         <f t="shared" si="4"/>
@@ -9758,7 +6683,7 @@
     </row>
     <row r="288" spans="2:5">
       <c r="B288" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C288" t="str">
         <f t="shared" si="4"/>
@@ -9773,7 +6698,7 @@
     </row>
     <row r="289" spans="2:5">
       <c r="B289" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C289" t="str">
         <f t="shared" si="4"/>
@@ -9788,7 +6713,7 @@
     </row>
     <row r="290" spans="2:5">
       <c r="B290" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C290" t="str">
         <f t="shared" si="4"/>
@@ -9803,7 +6728,7 @@
     </row>
     <row r="291" spans="2:5">
       <c r="B291" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C291" t="str">
         <f t="shared" si="4"/>
@@ -9818,7 +6743,7 @@
     </row>
     <row r="292" spans="2:5">
       <c r="B292" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C292" t="str">
         <f t="shared" si="4"/>
@@ -9833,7 +6758,7 @@
     </row>
     <row r="293" spans="2:5">
       <c r="B293" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C293" t="str">
         <f t="shared" si="4"/>
@@ -9848,7 +6773,7 @@
     </row>
     <row r="294" spans="2:5">
       <c r="B294" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C294" t="str">
         <f t="shared" si="4"/>
@@ -9863,7 +6788,7 @@
     </row>
     <row r="295" spans="2:5">
       <c r="B295" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C295" t="str">
         <f t="shared" si="4"/>
@@ -9878,7 +6803,7 @@
     </row>
     <row r="296" spans="2:5">
       <c r="B296" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C296" t="str">
         <f t="shared" si="4"/>
@@ -9893,7 +6818,7 @@
     </row>
     <row r="297" spans="2:5">
       <c r="B297" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C297" t="str">
         <f t="shared" si="4"/>
@@ -9908,7 +6833,7 @@
     </row>
     <row r="298" spans="2:5">
       <c r="B298" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C298" t="str">
         <f t="shared" si="4"/>
@@ -9923,7 +6848,7 @@
     </row>
     <row r="299" spans="2:5">
       <c r="B299" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C299" t="str">
         <f t="shared" si="4"/>
@@ -9938,7 +6863,7 @@
     </row>
     <row r="300" spans="2:5">
       <c r="B300" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C300" t="str">
         <f t="shared" si="4"/>
@@ -9953,7 +6878,7 @@
     </row>
     <row r="301" spans="2:5">
       <c r="B301" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C301" t="str">
         <f t="shared" si="4"/>
@@ -9968,7 +6893,7 @@
     </row>
     <row r="302" spans="2:5">
       <c r="B302" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C302" t="str">
         <f t="shared" si="4"/>
@@ -9983,7 +6908,7 @@
     </row>
     <row r="303" spans="2:5">
       <c r="B303" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C303" t="str">
         <f t="shared" si="4"/>
@@ -9998,7 +6923,7 @@
     </row>
     <row r="304" spans="2:5">
       <c r="B304" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C304" t="str">
         <f t="shared" si="4"/>
@@ -10013,7 +6938,7 @@
     </row>
     <row r="305" spans="2:5">
       <c r="B305" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C305" t="str">
         <f t="shared" si="4"/>
@@ -10028,7 +6953,7 @@
     </row>
     <row r="306" spans="2:5">
       <c r="B306" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C306" t="str">
         <f t="shared" si="4"/>
@@ -10043,7 +6968,7 @@
     </row>
     <row r="307" spans="2:5">
       <c r="B307" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C307" t="str">
         <f t="shared" si="4"/>
@@ -10058,7 +6983,7 @@
     </row>
     <row r="308" spans="2:5">
       <c r="B308" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C308" t="str">
         <f t="shared" si="4"/>
@@ -10073,7 +6998,7 @@
     </row>
     <row r="309" spans="2:5">
       <c r="B309" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C309" t="str">
         <f t="shared" si="4"/>
@@ -10088,7 +7013,7 @@
     </row>
     <row r="310" spans="2:5">
       <c r="B310" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C310" t="str">
         <f t="shared" si="4"/>
@@ -10103,7 +7028,7 @@
     </row>
     <row r="311" spans="2:5">
       <c r="B311" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C311" t="str">
         <f t="shared" si="4"/>
@@ -10118,7 +7043,7 @@
     </row>
     <row r="312" spans="2:5">
       <c r="B312" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C312" t="str">
         <f t="shared" si="4"/>
@@ -10133,7 +7058,7 @@
     </row>
     <row r="313" spans="2:5">
       <c r="B313" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C313" t="str">
         <f t="shared" si="4"/>
@@ -10148,7 +7073,7 @@
     </row>
     <row r="314" spans="2:5">
       <c r="B314" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C314" t="str">
         <f t="shared" si="4"/>
@@ -10163,7 +7088,7 @@
     </row>
     <row r="315" spans="2:5">
       <c r="B315" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C315" t="str">
         <f t="shared" si="4"/>
@@ -10178,7 +7103,7 @@
     </row>
     <row r="316" spans="2:5">
       <c r="B316" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C316" t="str">
         <f t="shared" si="4"/>
@@ -10193,7 +7118,7 @@
     </row>
     <row r="317" spans="2:5">
       <c r="B317" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C317" t="str">
         <f t="shared" si="4"/>
@@ -10208,7 +7133,7 @@
     </row>
     <row r="318" spans="2:5">
       <c r="B318" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C318" t="str">
         <f t="shared" si="4"/>
@@ -10223,7 +7148,7 @@
     </row>
     <row r="319" spans="2:5">
       <c r="B319" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C319" t="str">
         <f t="shared" si="4"/>
@@ -10238,7 +7163,7 @@
     </row>
     <row r="320" spans="2:5">
       <c r="B320" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C320" t="str">
         <f t="shared" si="4"/>
@@ -10253,7 +7178,7 @@
     </row>
     <row r="321" spans="2:5">
       <c r="B321" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="C321" t="str">
         <f t="shared" si="4"/>

--- a/models/demo-target/demo-target.xlsx
+++ b/models/demo-target/demo-target.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/shxie/projects/anse-models/demo-target/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB5A3652-D2FE-274A-B0F9-DC69A05B5674}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC9AE9E2-F500-3945-8E2B-36C99F307A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="600" windowWidth="25600" windowHeight="26880" activeTab="1" xr2:uid="{73351A0E-E394-C94F-8AB9-3EA9DA143F24}"/>
+    <workbookView xWindow="25600" yWindow="600" windowWidth="25600" windowHeight="26880" xr2:uid="{73351A0E-E394-C94F-8AB9-3EA9DA143F24}"/>
   </bookViews>
   <sheets>
     <sheet name="Inputs - Flow Network" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="Inputs - Spatial" sheetId="4" r:id="rId4"/>
     <sheet name="Inputs - Advanced Curves" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -44,6 +44,7 @@
   <authors>
     <author>Magnan, Michael</author>
     <author>mhafer</author>
+    <author>tc={BC27BDC6-B332-1E4A-B67A-FE37EEA862BB}</author>
   </authors>
   <commentList>
     <comment ref="D1" authorId="0" shapeId="0" xr:uid="{DE5AEED7-5306-0F41-A9F6-E09723C07087}">
@@ -380,27 +381,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="G47" authorId="0" shapeId="0" xr:uid="{9D0C205B-9C9C-3F4A-912F-B707A4FF980A}">
+    <comment ref="G47" authorId="2" shapeId="0" xr:uid="{BC27BDC6-B332-1E4A-B67A-FE37EEA862BB}">
       <text>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Magnan, Michael:
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    The physical state into which the C mass is transformed. Must supply a distinct Physical State here (not Physical State Group)
 </t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="11"/>
-            <color rgb="FF000000"/>
-            <rFont val="Helvetica Neue"/>
-            <family val="2"/>
-          </rPr>
-          <t>The physical state into which the C mass is transformed. Must supply a distinct Physical State here (not Physical State Group)</t>
-        </r>
       </text>
     </comment>
   </commentList>
@@ -767,18 +754,9 @@
     <t>Proportion</t>
   </si>
   <si>
-    <t>Target Amount (Double precison)</t>
-  </si>
-  <si>
     <t>New Physical State Name</t>
   </si>
   <si>
-    <t>Filter By Physical State Name/Group</t>
-  </si>
-  <si>
-    <t>Filter By Species Name/Group</t>
-  </si>
-  <si>
     <t>Note</t>
   </si>
   <si>
@@ -1002,13 +980,22 @@
   </si>
   <si>
     <t>Combusting</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Physical State Rule</t>
+  </si>
+  <si>
+    <t>Species Rule</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1044,8 +1031,14 @@
       <name val="HelveticaNeue"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1056,6 +1049,12 @@
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="65"/>
       </patternFill>
     </fill>
   </fills>
@@ -1071,12 +1070,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1113,6 +1113,12 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="Magnan, Michael" id="{01F42A6A-86CC-0D46-A8DC-97D0279EAF84}" userId="" providerId=""/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1430,6 +1436,15 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="G47" personId="{01F42A6A-86CC-0D46-A8DC-97D0279EAF84}" id="{BC27BDC6-B332-1E4A-B67A-FE37EEA862BB}">
+    <text xml:space="preserve">The physical state into which the C mass is transformed. Must supply a distinct Physical State here (not Physical State Group)
+</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F935C300-5F44-C54A-ADD4-2A504DCCAD49}">
   <dimension ref="B1:L61"/>
@@ -1674,26 +1689,26 @@
     </row>
     <row r="20" spans="2:7" ht="16" customHeight="1">
       <c r="B20" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C20" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="2:7" ht="16" customHeight="1">
       <c r="B21" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C21" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="22" spans="2:7" ht="16" customHeight="1">
       <c r="B22" t="s">
+        <v>112</v>
+      </c>
+      <c r="C22" t="s">
         <v>115</v>
-      </c>
-      <c r="C22" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="25" spans="2:7" s="3" customFormat="1" ht="16" customHeight="1">
@@ -2012,25 +2027,25 @@
       <c r="E47" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F47" s="3" t="s">
+      <c r="F47" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="G47" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G47" s="3" t="s">
+      <c r="H47" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I47" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="J47" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="49" spans="2:6" ht="16" customHeight="1">
       <c r="B49" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C49" t="str">
         <f>$C$43</f>
@@ -2046,7 +2061,7 @@
     </row>
     <row r="50" spans="2:6" ht="16" customHeight="1">
       <c r="B50" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C50" t="str">
         <f t="shared" ref="C50:C52" si="1">$C$43</f>
@@ -2062,7 +2077,7 @@
     </row>
     <row r="51" spans="2:6" ht="16" customHeight="1">
       <c r="B51" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C51" t="str">
         <f t="shared" si="1"/>
@@ -2078,7 +2093,7 @@
     </row>
     <row r="52" spans="2:6" ht="16" customHeight="1">
       <c r="B52" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C52" t="str">
         <f t="shared" si="1"/>
@@ -2094,7 +2109,7 @@
     </row>
     <row r="54" spans="2:6" ht="16" customHeight="1">
       <c r="B54" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C54" t="str">
         <f>$C$43</f>
@@ -2110,7 +2125,7 @@
     </row>
     <row r="55" spans="2:6" ht="16" customHeight="1">
       <c r="B55" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C55" t="str">
         <f t="shared" ref="C55:C57" si="4">$C$43</f>
@@ -2126,7 +2141,7 @@
     </row>
     <row r="56" spans="2:6" ht="16" customHeight="1">
       <c r="B56" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C56" t="str">
         <f t="shared" si="4"/>
@@ -2142,7 +2157,7 @@
     </row>
     <row r="57" spans="2:6" ht="16" customHeight="1">
       <c r="B57" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C57" t="str">
         <f t="shared" si="4"/>
@@ -2158,7 +2173,7 @@
     </row>
     <row r="59" spans="2:6" ht="16" customHeight="1">
       <c r="B59" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C59" t="str">
         <f>C45</f>
@@ -2173,7 +2188,7 @@
     </row>
     <row r="61" spans="2:6" ht="16" customHeight="1">
       <c r="B61" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C61" t="str" cm="1">
         <f t="array" ref="C61">C44</f>
@@ -2210,31 +2225,31 @@
   <sheetData>
     <row r="1" spans="2:11" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="H1" s="3" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>34</v>
@@ -2242,7 +2257,7 @@
     </row>
     <row r="2" spans="2:11">
       <c r="B2" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C2" t="str">
         <f>'Inputs - Flow Network'!$C$3</f>
@@ -2277,58 +2292,58 @@
   <sheetData>
     <row r="1" spans="2:7" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="2:7">
       <c r="B3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
     </row>
     <row r="4" spans="2:7">
       <c r="B4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="2:7">
       <c r="B5" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="2:7">
       <c r="B6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C6" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="7" spans="2:7">
       <c r="B7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="2:7" s="3" customFormat="1">
       <c r="B9" s="2" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>1</v>
@@ -2342,27 +2357,27 @@
     </row>
     <row r="11" spans="2:7" s="3" customFormat="1">
       <c r="B11" s="2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" spans="2:7" s="3" customFormat="1">
       <c r="B13" s="2" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>33</v>
@@ -2373,23 +2388,23 @@
     </row>
     <row r="15" spans="2:7">
       <c r="B15" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="2:7">
       <c r="B16" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="18" spans="2:5" s="3" customFormat="1">
       <c r="B18" s="2" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>1</v>
@@ -2403,24 +2418,24 @@
     </row>
     <row r="20" spans="2:5" s="3" customFormat="1">
       <c r="B20" s="2" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="22" spans="2:5" s="3" customFormat="1">
       <c r="B22" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>34</v>
@@ -2450,22 +2465,22 @@
   <sheetData>
     <row r="1" spans="2:8" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="D1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="H1" s="3" t="s">
         <v>34</v>
@@ -2473,13 +2488,13 @@
     </row>
     <row r="2" spans="2:8">
       <c r="B2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="E2">
         <v>998</v>
@@ -2487,7 +2502,7 @@
     </row>
     <row r="5" spans="2:8" s="3" customFormat="1">
       <c r="B5" s="2" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>1</v>
@@ -2495,21 +2510,21 @@
     </row>
     <row r="6" spans="2:8">
       <c r="B6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8" spans="2:8" s="3" customFormat="1">
       <c r="B8" s="2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>34</v>
@@ -2517,10 +2532,10 @@
     </row>
     <row r="10" spans="2:8">
       <c r="B10" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C10" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D10" t="str">
         <f>C6</f>
@@ -2529,21 +2544,21 @@
     </row>
     <row r="13" spans="2:8" s="3" customFormat="1">
       <c r="B13" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="14" spans="2:8">
       <c r="B14" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C14" t="str">
         <f>C10</f>
@@ -2575,13 +2590,13 @@
   <sheetData>
     <row r="1" spans="2:6" s="3" customFormat="1">
       <c r="B1" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E1" s="3" t="s">
         <v>33</v>
@@ -2592,21 +2607,21 @@
     </row>
     <row r="3" spans="2:6">
       <c r="B3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="C3" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
     </row>
     <row r="7" spans="2:6" s="3" customFormat="1">
       <c r="B7" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>1</v>
@@ -2620,32 +2635,32 @@
     </row>
     <row r="9" spans="2:6">
       <c r="B9" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C9" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="12" spans="2:6" s="3" customFormat="1">
       <c r="B12" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>19</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="2:6">
       <c r="B14" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C14" t="str">
         <f>C9</f>
@@ -2664,21 +2679,21 @@
     </row>
     <row r="19" spans="2:5" s="3" customFormat="1">
       <c r="B19" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="E19" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="21" spans="2:5">
       <c r="B21" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C21" t="str">
         <f>$C$3</f>
@@ -2693,7 +2708,7 @@
     </row>
     <row r="22" spans="2:5">
       <c r="B22" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C22" t="str">
         <f t="shared" ref="C22:C85" si="0">$C$3</f>
@@ -2708,7 +2723,7 @@
     </row>
     <row r="23" spans="2:5">
       <c r="B23" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C23" t="str">
         <f t="shared" si="0"/>
@@ -2723,7 +2738,7 @@
     </row>
     <row r="24" spans="2:5">
       <c r="B24" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C24" t="str">
         <f t="shared" si="0"/>
@@ -2738,7 +2753,7 @@
     </row>
     <row r="25" spans="2:5">
       <c r="B25" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C25" t="str">
         <f t="shared" si="0"/>
@@ -2753,7 +2768,7 @@
     </row>
     <row r="26" spans="2:5">
       <c r="B26" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C26" t="str">
         <f t="shared" si="0"/>
@@ -2768,7 +2783,7 @@
     </row>
     <row r="27" spans="2:5">
       <c r="B27" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C27" t="str">
         <f t="shared" si="0"/>
@@ -2783,7 +2798,7 @@
     </row>
     <row r="28" spans="2:5">
       <c r="B28" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C28" t="str">
         <f t="shared" si="0"/>
@@ -2798,7 +2813,7 @@
     </row>
     <row r="29" spans="2:5">
       <c r="B29" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C29" t="str">
         <f t="shared" si="0"/>
@@ -2813,7 +2828,7 @@
     </row>
     <row r="30" spans="2:5">
       <c r="B30" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C30" t="str">
         <f t="shared" si="0"/>
@@ -2828,7 +2843,7 @@
     </row>
     <row r="31" spans="2:5">
       <c r="B31" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C31" t="str">
         <f t="shared" si="0"/>
@@ -2843,7 +2858,7 @@
     </row>
     <row r="32" spans="2:5">
       <c r="B32" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C32" t="str">
         <f t="shared" si="0"/>
@@ -2858,7 +2873,7 @@
     </row>
     <row r="33" spans="2:5">
       <c r="B33" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C33" t="str">
         <f t="shared" si="0"/>
@@ -2873,7 +2888,7 @@
     </row>
     <row r="34" spans="2:5">
       <c r="B34" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C34" t="str">
         <f t="shared" si="0"/>
@@ -2888,7 +2903,7 @@
     </row>
     <row r="35" spans="2:5">
       <c r="B35" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C35" t="str">
         <f t="shared" si="0"/>
@@ -2903,7 +2918,7 @@
     </row>
     <row r="36" spans="2:5">
       <c r="B36" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C36" t="str">
         <f t="shared" si="0"/>
@@ -2918,7 +2933,7 @@
     </row>
     <row r="37" spans="2:5">
       <c r="B37" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C37" t="str">
         <f t="shared" si="0"/>
@@ -2933,7 +2948,7 @@
     </row>
     <row r="38" spans="2:5">
       <c r="B38" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C38" t="str">
         <f t="shared" si="0"/>
@@ -2948,7 +2963,7 @@
     </row>
     <row r="39" spans="2:5">
       <c r="B39" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C39" t="str">
         <f t="shared" si="0"/>
@@ -2963,7 +2978,7 @@
     </row>
     <row r="40" spans="2:5">
       <c r="B40" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C40" t="str">
         <f t="shared" si="0"/>
@@ -2978,7 +2993,7 @@
     </row>
     <row r="41" spans="2:5">
       <c r="B41" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C41" t="str">
         <f t="shared" si="0"/>
@@ -2993,7 +3008,7 @@
     </row>
     <row r="42" spans="2:5">
       <c r="B42" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C42" t="str">
         <f t="shared" si="0"/>
@@ -3008,7 +3023,7 @@
     </row>
     <row r="43" spans="2:5">
       <c r="B43" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C43" t="str">
         <f t="shared" si="0"/>
@@ -3023,7 +3038,7 @@
     </row>
     <row r="44" spans="2:5">
       <c r="B44" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C44" t="str">
         <f t="shared" si="0"/>
@@ -3038,7 +3053,7 @@
     </row>
     <row r="45" spans="2:5">
       <c r="B45" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C45" t="str">
         <f t="shared" si="0"/>
@@ -3053,7 +3068,7 @@
     </row>
     <row r="46" spans="2:5">
       <c r="B46" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C46" t="str">
         <f t="shared" si="0"/>
@@ -3068,7 +3083,7 @@
     </row>
     <row r="47" spans="2:5">
       <c r="B47" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C47" t="str">
         <f t="shared" si="0"/>
@@ -3083,7 +3098,7 @@
     </row>
     <row r="48" spans="2:5">
       <c r="B48" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C48" t="str">
         <f t="shared" si="0"/>
@@ -3098,7 +3113,7 @@
     </row>
     <row r="49" spans="2:5">
       <c r="B49" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C49" t="str">
         <f t="shared" si="0"/>
@@ -3113,7 +3128,7 @@
     </row>
     <row r="50" spans="2:5">
       <c r="B50" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C50" t="str">
         <f t="shared" si="0"/>
@@ -3128,7 +3143,7 @@
     </row>
     <row r="51" spans="2:5">
       <c r="B51" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C51" t="str">
         <f t="shared" si="0"/>
@@ -3143,7 +3158,7 @@
     </row>
     <row r="52" spans="2:5">
       <c r="B52" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C52" t="str">
         <f t="shared" si="0"/>
@@ -3158,7 +3173,7 @@
     </row>
     <row r="53" spans="2:5">
       <c r="B53" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C53" t="str">
         <f t="shared" si="0"/>
@@ -3173,7 +3188,7 @@
     </row>
     <row r="54" spans="2:5">
       <c r="B54" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C54" t="str">
         <f t="shared" si="0"/>
@@ -3188,7 +3203,7 @@
     </row>
     <row r="55" spans="2:5">
       <c r="B55" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C55" t="str">
         <f t="shared" si="0"/>
@@ -3203,7 +3218,7 @@
     </row>
     <row r="56" spans="2:5">
       <c r="B56" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C56" t="str">
         <f t="shared" si="0"/>
@@ -3218,7 +3233,7 @@
     </row>
     <row r="57" spans="2:5">
       <c r="B57" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C57" t="str">
         <f t="shared" si="0"/>
@@ -3233,7 +3248,7 @@
     </row>
     <row r="58" spans="2:5">
       <c r="B58" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C58" t="str">
         <f t="shared" si="0"/>
@@ -3248,7 +3263,7 @@
     </row>
     <row r="59" spans="2:5">
       <c r="B59" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C59" t="str">
         <f t="shared" si="0"/>
@@ -3263,7 +3278,7 @@
     </row>
     <row r="60" spans="2:5">
       <c r="B60" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C60" t="str">
         <f t="shared" si="0"/>
@@ -3278,7 +3293,7 @@
     </row>
     <row r="61" spans="2:5">
       <c r="B61" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C61" t="str">
         <f t="shared" si="0"/>
@@ -3293,7 +3308,7 @@
     </row>
     <row r="62" spans="2:5">
       <c r="B62" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C62" t="str">
         <f t="shared" si="0"/>
@@ -3308,7 +3323,7 @@
     </row>
     <row r="63" spans="2:5">
       <c r="B63" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C63" t="str">
         <f t="shared" si="0"/>
@@ -3323,7 +3338,7 @@
     </row>
     <row r="64" spans="2:5">
       <c r="B64" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C64" t="str">
         <f t="shared" si="0"/>
@@ -3338,7 +3353,7 @@
     </row>
     <row r="65" spans="2:5">
       <c r="B65" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C65" t="str">
         <f t="shared" si="0"/>
@@ -3353,7 +3368,7 @@
     </row>
     <row r="66" spans="2:5">
       <c r="B66" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C66" t="str">
         <f t="shared" si="0"/>
@@ -3368,7 +3383,7 @@
     </row>
     <row r="67" spans="2:5">
       <c r="B67" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C67" t="str">
         <f t="shared" si="0"/>
@@ -3383,7 +3398,7 @@
     </row>
     <row r="68" spans="2:5">
       <c r="B68" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C68" t="str">
         <f t="shared" si="0"/>
@@ -3398,7 +3413,7 @@
     </row>
     <row r="69" spans="2:5">
       <c r="B69" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C69" t="str">
         <f t="shared" si="0"/>
@@ -3413,7 +3428,7 @@
     </row>
     <row r="70" spans="2:5">
       <c r="B70" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C70" t="str">
         <f t="shared" si="0"/>
@@ -3428,7 +3443,7 @@
     </row>
     <row r="71" spans="2:5">
       <c r="B71" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C71" t="str">
         <f t="shared" si="0"/>
@@ -3443,7 +3458,7 @@
     </row>
     <row r="72" spans="2:5">
       <c r="B72" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C72" t="str">
         <f t="shared" si="0"/>
@@ -3458,7 +3473,7 @@
     </row>
     <row r="73" spans="2:5">
       <c r="B73" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C73" t="str">
         <f t="shared" si="0"/>
@@ -3473,7 +3488,7 @@
     </row>
     <row r="74" spans="2:5">
       <c r="B74" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C74" t="str">
         <f t="shared" si="0"/>
@@ -3488,7 +3503,7 @@
     </row>
     <row r="75" spans="2:5">
       <c r="B75" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C75" t="str">
         <f t="shared" si="0"/>
@@ -3503,7 +3518,7 @@
     </row>
     <row r="76" spans="2:5">
       <c r="B76" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C76" t="str">
         <f t="shared" si="0"/>
@@ -3518,7 +3533,7 @@
     </row>
     <row r="77" spans="2:5">
       <c r="B77" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C77" t="str">
         <f t="shared" si="0"/>
@@ -3533,7 +3548,7 @@
     </row>
     <row r="78" spans="2:5">
       <c r="B78" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C78" t="str">
         <f t="shared" si="0"/>
@@ -3548,7 +3563,7 @@
     </row>
     <row r="79" spans="2:5">
       <c r="B79" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C79" t="str">
         <f t="shared" si="0"/>
@@ -3563,7 +3578,7 @@
     </row>
     <row r="80" spans="2:5">
       <c r="B80" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C80" t="str">
         <f t="shared" si="0"/>
@@ -3578,7 +3593,7 @@
     </row>
     <row r="81" spans="2:5">
       <c r="B81" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C81" t="str">
         <f t="shared" si="0"/>
@@ -3593,7 +3608,7 @@
     </row>
     <row r="82" spans="2:5">
       <c r="B82" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C82" t="str">
         <f t="shared" si="0"/>
@@ -3608,7 +3623,7 @@
     </row>
     <row r="83" spans="2:5">
       <c r="B83" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C83" t="str">
         <f t="shared" si="0"/>
@@ -3623,7 +3638,7 @@
     </row>
     <row r="84" spans="2:5">
       <c r="B84" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C84" t="str">
         <f t="shared" si="0"/>
@@ -3638,7 +3653,7 @@
     </row>
     <row r="85" spans="2:5">
       <c r="B85" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C85" t="str">
         <f t="shared" si="0"/>
@@ -3653,7 +3668,7 @@
     </row>
     <row r="86" spans="2:5">
       <c r="B86" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C86" t="str">
         <f t="shared" ref="C86:C149" si="1">$C$3</f>
@@ -3668,7 +3683,7 @@
     </row>
     <row r="87" spans="2:5">
       <c r="B87" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C87" t="str">
         <f t="shared" si="1"/>
@@ -3683,7 +3698,7 @@
     </row>
     <row r="88" spans="2:5">
       <c r="B88" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C88" t="str">
         <f t="shared" si="1"/>
@@ -3698,7 +3713,7 @@
     </row>
     <row r="89" spans="2:5">
       <c r="B89" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C89" t="str">
         <f t="shared" si="1"/>
@@ -3713,7 +3728,7 @@
     </row>
     <row r="90" spans="2:5">
       <c r="B90" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C90" t="str">
         <f t="shared" si="1"/>
@@ -3728,7 +3743,7 @@
     </row>
     <row r="91" spans="2:5">
       <c r="B91" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C91" t="str">
         <f t="shared" si="1"/>
@@ -3743,7 +3758,7 @@
     </row>
     <row r="92" spans="2:5">
       <c r="B92" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C92" t="str">
         <f t="shared" si="1"/>
@@ -3758,7 +3773,7 @@
     </row>
     <row r="93" spans="2:5">
       <c r="B93" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C93" t="str">
         <f t="shared" si="1"/>
@@ -3773,7 +3788,7 @@
     </row>
     <row r="94" spans="2:5">
       <c r="B94" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C94" t="str">
         <f t="shared" si="1"/>
@@ -3788,7 +3803,7 @@
     </row>
     <row r="95" spans="2:5">
       <c r="B95" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C95" t="str">
         <f t="shared" si="1"/>
@@ -3803,7 +3818,7 @@
     </row>
     <row r="96" spans="2:5">
       <c r="B96" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C96" t="str">
         <f t="shared" si="1"/>
@@ -3818,7 +3833,7 @@
     </row>
     <row r="97" spans="2:5">
       <c r="B97" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C97" t="str">
         <f t="shared" si="1"/>
@@ -3833,7 +3848,7 @@
     </row>
     <row r="98" spans="2:5">
       <c r="B98" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C98" t="str">
         <f t="shared" si="1"/>
@@ -3848,7 +3863,7 @@
     </row>
     <row r="99" spans="2:5">
       <c r="B99" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C99" t="str">
         <f t="shared" si="1"/>
@@ -3863,7 +3878,7 @@
     </row>
     <row r="100" spans="2:5">
       <c r="B100" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C100" t="str">
         <f t="shared" si="1"/>
@@ -3878,7 +3893,7 @@
     </row>
     <row r="101" spans="2:5">
       <c r="B101" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C101" t="str">
         <f t="shared" si="1"/>
@@ -3893,7 +3908,7 @@
     </row>
     <row r="102" spans="2:5">
       <c r="B102" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C102" t="str">
         <f t="shared" si="1"/>
@@ -3908,7 +3923,7 @@
     </row>
     <row r="103" spans="2:5">
       <c r="B103" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C103" t="str">
         <f t="shared" si="1"/>
@@ -3923,7 +3938,7 @@
     </row>
     <row r="104" spans="2:5">
       <c r="B104" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C104" t="str">
         <f t="shared" si="1"/>
@@ -3938,7 +3953,7 @@
     </row>
     <row r="105" spans="2:5">
       <c r="B105" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C105" t="str">
         <f t="shared" si="1"/>
@@ -3953,7 +3968,7 @@
     </row>
     <row r="106" spans="2:5">
       <c r="B106" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C106" t="str">
         <f t="shared" si="1"/>
@@ -3968,7 +3983,7 @@
     </row>
     <row r="107" spans="2:5">
       <c r="B107" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C107" t="str">
         <f t="shared" si="1"/>
@@ -3983,7 +3998,7 @@
     </row>
     <row r="108" spans="2:5">
       <c r="B108" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C108" t="str">
         <f t="shared" si="1"/>
@@ -3998,7 +4013,7 @@
     </row>
     <row r="109" spans="2:5">
       <c r="B109" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C109" t="str">
         <f t="shared" si="1"/>
@@ -4013,7 +4028,7 @@
     </row>
     <row r="110" spans="2:5">
       <c r="B110" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C110" t="str">
         <f t="shared" si="1"/>
@@ -4028,7 +4043,7 @@
     </row>
     <row r="111" spans="2:5">
       <c r="B111" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C111" t="str">
         <f t="shared" si="1"/>
@@ -4043,7 +4058,7 @@
     </row>
     <row r="112" spans="2:5">
       <c r="B112" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C112" t="str">
         <f t="shared" si="1"/>
@@ -4058,7 +4073,7 @@
     </row>
     <row r="113" spans="2:5">
       <c r="B113" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C113" t="str">
         <f t="shared" si="1"/>
@@ -4073,7 +4088,7 @@
     </row>
     <row r="114" spans="2:5">
       <c r="B114" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C114" t="str">
         <f t="shared" si="1"/>
@@ -4088,7 +4103,7 @@
     </row>
     <row r="115" spans="2:5">
       <c r="B115" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C115" t="str">
         <f t="shared" si="1"/>
@@ -4103,7 +4118,7 @@
     </row>
     <row r="116" spans="2:5">
       <c r="B116" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C116" t="str">
         <f t="shared" si="1"/>
@@ -4118,7 +4133,7 @@
     </row>
     <row r="117" spans="2:5">
       <c r="B117" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C117" t="str">
         <f t="shared" si="1"/>
@@ -4133,7 +4148,7 @@
     </row>
     <row r="118" spans="2:5">
       <c r="B118" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C118" t="str">
         <f t="shared" si="1"/>
@@ -4148,7 +4163,7 @@
     </row>
     <row r="119" spans="2:5">
       <c r="B119" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C119" t="str">
         <f t="shared" si="1"/>
@@ -4163,7 +4178,7 @@
     </row>
     <row r="120" spans="2:5">
       <c r="B120" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C120" t="str">
         <f t="shared" si="1"/>
@@ -4178,7 +4193,7 @@
     </row>
     <row r="121" spans="2:5">
       <c r="B121" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C121" t="str">
         <f t="shared" si="1"/>
@@ -4193,7 +4208,7 @@
     </row>
     <row r="122" spans="2:5">
       <c r="B122" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C122" t="str">
         <f t="shared" si="1"/>
@@ -4208,7 +4223,7 @@
     </row>
     <row r="123" spans="2:5">
       <c r="B123" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C123" t="str">
         <f t="shared" si="1"/>
@@ -4223,7 +4238,7 @@
     </row>
     <row r="124" spans="2:5">
       <c r="B124" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C124" t="str">
         <f t="shared" si="1"/>
@@ -4238,7 +4253,7 @@
     </row>
     <row r="125" spans="2:5">
       <c r="B125" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C125" t="str">
         <f t="shared" si="1"/>
@@ -4253,7 +4268,7 @@
     </row>
     <row r="126" spans="2:5">
       <c r="B126" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C126" t="str">
         <f t="shared" si="1"/>
@@ -4268,7 +4283,7 @@
     </row>
     <row r="127" spans="2:5">
       <c r="B127" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C127" t="str">
         <f t="shared" si="1"/>
@@ -4283,7 +4298,7 @@
     </row>
     <row r="128" spans="2:5">
       <c r="B128" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C128" t="str">
         <f t="shared" si="1"/>
@@ -4298,7 +4313,7 @@
     </row>
     <row r="129" spans="2:5">
       <c r="B129" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C129" t="str">
         <f t="shared" si="1"/>
@@ -4313,7 +4328,7 @@
     </row>
     <row r="130" spans="2:5">
       <c r="B130" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C130" t="str">
         <f t="shared" si="1"/>
@@ -4328,7 +4343,7 @@
     </row>
     <row r="131" spans="2:5">
       <c r="B131" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C131" t="str">
         <f t="shared" si="1"/>
@@ -4343,7 +4358,7 @@
     </row>
     <row r="132" spans="2:5">
       <c r="B132" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C132" t="str">
         <f t="shared" si="1"/>
@@ -4358,7 +4373,7 @@
     </row>
     <row r="133" spans="2:5">
       <c r="B133" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C133" t="str">
         <f t="shared" si="1"/>
@@ -4373,7 +4388,7 @@
     </row>
     <row r="134" spans="2:5">
       <c r="B134" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C134" t="str">
         <f t="shared" si="1"/>
@@ -4388,7 +4403,7 @@
     </row>
     <row r="135" spans="2:5">
       <c r="B135" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C135" t="str">
         <f t="shared" si="1"/>
@@ -4403,7 +4418,7 @@
     </row>
     <row r="136" spans="2:5">
       <c r="B136" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C136" t="str">
         <f t="shared" si="1"/>
@@ -4418,7 +4433,7 @@
     </row>
     <row r="137" spans="2:5">
       <c r="B137" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C137" t="str">
         <f t="shared" si="1"/>
@@ -4433,7 +4448,7 @@
     </row>
     <row r="138" spans="2:5">
       <c r="B138" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C138" t="str">
         <f t="shared" si="1"/>
@@ -4448,7 +4463,7 @@
     </row>
     <row r="139" spans="2:5">
       <c r="B139" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C139" t="str">
         <f t="shared" si="1"/>
@@ -4463,7 +4478,7 @@
     </row>
     <row r="140" spans="2:5">
       <c r="B140" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C140" t="str">
         <f t="shared" si="1"/>
@@ -4478,7 +4493,7 @@
     </row>
     <row r="141" spans="2:5">
       <c r="B141" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C141" t="str">
         <f t="shared" si="1"/>
@@ -4493,7 +4508,7 @@
     </row>
     <row r="142" spans="2:5">
       <c r="B142" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C142" t="str">
         <f t="shared" si="1"/>
@@ -4508,7 +4523,7 @@
     </row>
     <row r="143" spans="2:5">
       <c r="B143" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C143" t="str">
         <f t="shared" si="1"/>
@@ -4523,7 +4538,7 @@
     </row>
     <row r="144" spans="2:5">
       <c r="B144" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C144" t="str">
         <f t="shared" si="1"/>
@@ -4538,7 +4553,7 @@
     </row>
     <row r="145" spans="2:5">
       <c r="B145" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C145" t="str">
         <f t="shared" si="1"/>
@@ -4553,7 +4568,7 @@
     </row>
     <row r="146" spans="2:5">
       <c r="B146" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C146" t="str">
         <f t="shared" si="1"/>
@@ -4568,7 +4583,7 @@
     </row>
     <row r="147" spans="2:5">
       <c r="B147" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C147" t="str">
         <f t="shared" si="1"/>
@@ -4583,7 +4598,7 @@
     </row>
     <row r="148" spans="2:5">
       <c r="B148" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C148" t="str">
         <f t="shared" si="1"/>
@@ -4598,7 +4613,7 @@
     </row>
     <row r="149" spans="2:5">
       <c r="B149" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C149" t="str">
         <f t="shared" si="1"/>
@@ -4613,7 +4628,7 @@
     </row>
     <row r="150" spans="2:5">
       <c r="B150" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C150" t="str">
         <f t="shared" ref="C150:C213" si="2">$C$3</f>
@@ -4628,7 +4643,7 @@
     </row>
     <row r="151" spans="2:5">
       <c r="B151" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C151" t="str">
         <f t="shared" si="2"/>
@@ -4643,7 +4658,7 @@
     </row>
     <row r="152" spans="2:5">
       <c r="B152" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C152" t="str">
         <f t="shared" si="2"/>
@@ -4658,7 +4673,7 @@
     </row>
     <row r="153" spans="2:5">
       <c r="B153" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C153" t="str">
         <f t="shared" si="2"/>
@@ -4673,7 +4688,7 @@
     </row>
     <row r="154" spans="2:5">
       <c r="B154" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C154" t="str">
         <f t="shared" si="2"/>
@@ -4688,7 +4703,7 @@
     </row>
     <row r="155" spans="2:5">
       <c r="B155" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C155" t="str">
         <f t="shared" si="2"/>
@@ -4703,7 +4718,7 @@
     </row>
     <row r="156" spans="2:5">
       <c r="B156" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C156" t="str">
         <f t="shared" si="2"/>
@@ -4718,7 +4733,7 @@
     </row>
     <row r="157" spans="2:5">
       <c r="B157" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C157" t="str">
         <f t="shared" si="2"/>
@@ -4733,7 +4748,7 @@
     </row>
     <row r="158" spans="2:5">
       <c r="B158" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C158" t="str">
         <f t="shared" si="2"/>
@@ -4748,7 +4763,7 @@
     </row>
     <row r="159" spans="2:5">
       <c r="B159" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C159" t="str">
         <f t="shared" si="2"/>
@@ -4763,7 +4778,7 @@
     </row>
     <row r="160" spans="2:5">
       <c r="B160" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C160" t="str">
         <f t="shared" si="2"/>
@@ -4778,7 +4793,7 @@
     </row>
     <row r="161" spans="2:5">
       <c r="B161" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C161" t="str">
         <f t="shared" si="2"/>
@@ -4793,7 +4808,7 @@
     </row>
     <row r="162" spans="2:5">
       <c r="B162" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C162" t="str">
         <f t="shared" si="2"/>
@@ -4808,7 +4823,7 @@
     </row>
     <row r="163" spans="2:5">
       <c r="B163" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C163" t="str">
         <f t="shared" si="2"/>
@@ -4823,7 +4838,7 @@
     </row>
     <row r="164" spans="2:5">
       <c r="B164" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C164" t="str">
         <f t="shared" si="2"/>
@@ -4838,7 +4853,7 @@
     </row>
     <row r="165" spans="2:5">
       <c r="B165" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C165" t="str">
         <f t="shared" si="2"/>
@@ -4853,7 +4868,7 @@
     </row>
     <row r="166" spans="2:5">
       <c r="B166" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C166" t="str">
         <f t="shared" si="2"/>
@@ -4868,7 +4883,7 @@
     </row>
     <row r="167" spans="2:5">
       <c r="B167" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C167" t="str">
         <f t="shared" si="2"/>
@@ -4883,7 +4898,7 @@
     </row>
     <row r="168" spans="2:5">
       <c r="B168" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C168" t="str">
         <f t="shared" si="2"/>
@@ -4898,7 +4913,7 @@
     </row>
     <row r="169" spans="2:5">
       <c r="B169" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C169" t="str">
         <f t="shared" si="2"/>
@@ -4913,7 +4928,7 @@
     </row>
     <row r="170" spans="2:5">
       <c r="B170" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C170" t="str">
         <f t="shared" si="2"/>
@@ -4928,7 +4943,7 @@
     </row>
     <row r="171" spans="2:5">
       <c r="B171" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C171" t="str">
         <f t="shared" si="2"/>
@@ -4943,7 +4958,7 @@
     </row>
     <row r="172" spans="2:5">
       <c r="B172" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C172" t="str">
         <f t="shared" si="2"/>
@@ -4958,7 +4973,7 @@
     </row>
     <row r="173" spans="2:5">
       <c r="B173" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C173" t="str">
         <f t="shared" si="2"/>
@@ -4973,7 +4988,7 @@
     </row>
     <row r="174" spans="2:5">
       <c r="B174" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C174" t="str">
         <f t="shared" si="2"/>
@@ -4988,7 +5003,7 @@
     </row>
     <row r="175" spans="2:5">
       <c r="B175" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C175" t="str">
         <f t="shared" si="2"/>
@@ -5003,7 +5018,7 @@
     </row>
     <row r="176" spans="2:5">
       <c r="B176" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C176" t="str">
         <f t="shared" si="2"/>
@@ -5018,7 +5033,7 @@
     </row>
     <row r="177" spans="2:5">
       <c r="B177" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C177" t="str">
         <f t="shared" si="2"/>
@@ -5033,7 +5048,7 @@
     </row>
     <row r="178" spans="2:5">
       <c r="B178" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C178" t="str">
         <f t="shared" si="2"/>
@@ -5048,7 +5063,7 @@
     </row>
     <row r="179" spans="2:5">
       <c r="B179" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C179" t="str">
         <f t="shared" si="2"/>
@@ -5063,7 +5078,7 @@
     </row>
     <row r="180" spans="2:5">
       <c r="B180" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C180" t="str">
         <f t="shared" si="2"/>
@@ -5078,7 +5093,7 @@
     </row>
     <row r="181" spans="2:5">
       <c r="B181" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C181" t="str">
         <f t="shared" si="2"/>
@@ -5093,7 +5108,7 @@
     </row>
     <row r="182" spans="2:5">
       <c r="B182" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C182" t="str">
         <f t="shared" si="2"/>
@@ -5108,7 +5123,7 @@
     </row>
     <row r="183" spans="2:5">
       <c r="B183" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C183" t="str">
         <f t="shared" si="2"/>
@@ -5123,7 +5138,7 @@
     </row>
     <row r="184" spans="2:5">
       <c r="B184" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C184" t="str">
         <f t="shared" si="2"/>
@@ -5138,7 +5153,7 @@
     </row>
     <row r="185" spans="2:5">
       <c r="B185" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C185" t="str">
         <f t="shared" si="2"/>
@@ -5153,7 +5168,7 @@
     </row>
     <row r="186" spans="2:5">
       <c r="B186" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C186" t="str">
         <f t="shared" si="2"/>
@@ -5168,7 +5183,7 @@
     </row>
     <row r="187" spans="2:5">
       <c r="B187" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C187" t="str">
         <f t="shared" si="2"/>
@@ -5183,7 +5198,7 @@
     </row>
     <row r="188" spans="2:5">
       <c r="B188" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C188" t="str">
         <f t="shared" si="2"/>
@@ -5198,7 +5213,7 @@
     </row>
     <row r="189" spans="2:5">
       <c r="B189" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C189" t="str">
         <f t="shared" si="2"/>
@@ -5213,7 +5228,7 @@
     </row>
     <row r="190" spans="2:5">
       <c r="B190" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C190" t="str">
         <f t="shared" si="2"/>
@@ -5228,7 +5243,7 @@
     </row>
     <row r="191" spans="2:5">
       <c r="B191" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C191" t="str">
         <f t="shared" si="2"/>
@@ -5243,7 +5258,7 @@
     </row>
     <row r="192" spans="2:5">
       <c r="B192" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C192" t="str">
         <f t="shared" si="2"/>
@@ -5258,7 +5273,7 @@
     </row>
     <row r="193" spans="2:5">
       <c r="B193" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C193" t="str">
         <f t="shared" si="2"/>
@@ -5273,7 +5288,7 @@
     </row>
     <row r="194" spans="2:5">
       <c r="B194" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C194" t="str">
         <f t="shared" si="2"/>
@@ -5288,7 +5303,7 @@
     </row>
     <row r="195" spans="2:5">
       <c r="B195" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C195" t="str">
         <f t="shared" si="2"/>
@@ -5303,7 +5318,7 @@
     </row>
     <row r="196" spans="2:5">
       <c r="B196" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C196" t="str">
         <f t="shared" si="2"/>
@@ -5318,7 +5333,7 @@
     </row>
     <row r="197" spans="2:5">
       <c r="B197" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C197" t="str">
         <f t="shared" si="2"/>
@@ -5333,7 +5348,7 @@
     </row>
     <row r="198" spans="2:5">
       <c r="B198" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C198" t="str">
         <f t="shared" si="2"/>
@@ -5348,7 +5363,7 @@
     </row>
     <row r="199" spans="2:5">
       <c r="B199" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C199" t="str">
         <f t="shared" si="2"/>
@@ -5363,7 +5378,7 @@
     </row>
     <row r="200" spans="2:5">
       <c r="B200" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C200" t="str">
         <f t="shared" si="2"/>
@@ -5378,7 +5393,7 @@
     </row>
     <row r="201" spans="2:5">
       <c r="B201" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C201" t="str">
         <f t="shared" si="2"/>
@@ -5393,7 +5408,7 @@
     </row>
     <row r="202" spans="2:5">
       <c r="B202" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C202" t="str">
         <f t="shared" si="2"/>
@@ -5408,7 +5423,7 @@
     </row>
     <row r="203" spans="2:5">
       <c r="B203" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C203" t="str">
         <f t="shared" si="2"/>
@@ -5423,7 +5438,7 @@
     </row>
     <row r="204" spans="2:5">
       <c r="B204" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C204" t="str">
         <f t="shared" si="2"/>
@@ -5438,7 +5453,7 @@
     </row>
     <row r="205" spans="2:5">
       <c r="B205" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C205" t="str">
         <f t="shared" si="2"/>
@@ -5453,7 +5468,7 @@
     </row>
     <row r="206" spans="2:5">
       <c r="B206" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C206" t="str">
         <f t="shared" si="2"/>
@@ -5468,7 +5483,7 @@
     </row>
     <row r="207" spans="2:5">
       <c r="B207" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C207" t="str">
         <f t="shared" si="2"/>
@@ -5483,7 +5498,7 @@
     </row>
     <row r="208" spans="2:5">
       <c r="B208" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C208" t="str">
         <f t="shared" si="2"/>
@@ -5498,7 +5513,7 @@
     </row>
     <row r="209" spans="2:5">
       <c r="B209" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C209" t="str">
         <f t="shared" si="2"/>
@@ -5513,7 +5528,7 @@
     </row>
     <row r="210" spans="2:5">
       <c r="B210" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C210" t="str">
         <f t="shared" si="2"/>
@@ -5528,7 +5543,7 @@
     </row>
     <row r="211" spans="2:5">
       <c r="B211" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C211" t="str">
         <f t="shared" si="2"/>
@@ -5543,7 +5558,7 @@
     </row>
     <row r="212" spans="2:5">
       <c r="B212" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C212" t="str">
         <f t="shared" si="2"/>
@@ -5558,7 +5573,7 @@
     </row>
     <row r="213" spans="2:5">
       <c r="B213" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C213" t="str">
         <f t="shared" si="2"/>
@@ -5573,7 +5588,7 @@
     </row>
     <row r="214" spans="2:5">
       <c r="B214" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C214" t="str">
         <f t="shared" ref="C214:C277" si="3">$C$3</f>
@@ -5588,7 +5603,7 @@
     </row>
     <row r="215" spans="2:5">
       <c r="B215" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C215" t="str">
         <f t="shared" si="3"/>
@@ -5603,7 +5618,7 @@
     </row>
     <row r="216" spans="2:5">
       <c r="B216" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C216" t="str">
         <f t="shared" si="3"/>
@@ -5618,7 +5633,7 @@
     </row>
     <row r="217" spans="2:5">
       <c r="B217" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C217" t="str">
         <f t="shared" si="3"/>
@@ -5633,7 +5648,7 @@
     </row>
     <row r="218" spans="2:5">
       <c r="B218" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C218" t="str">
         <f t="shared" si="3"/>
@@ -5648,7 +5663,7 @@
     </row>
     <row r="219" spans="2:5">
       <c r="B219" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C219" t="str">
         <f t="shared" si="3"/>
@@ -5663,7 +5678,7 @@
     </row>
     <row r="220" spans="2:5">
       <c r="B220" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C220" t="str">
         <f t="shared" si="3"/>
@@ -5678,7 +5693,7 @@
     </row>
     <row r="221" spans="2:5">
       <c r="B221" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C221" t="str">
         <f t="shared" si="3"/>
@@ -5693,7 +5708,7 @@
     </row>
     <row r="222" spans="2:5">
       <c r="B222" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C222" t="str">
         <f t="shared" si="3"/>
@@ -5708,7 +5723,7 @@
     </row>
     <row r="223" spans="2:5">
       <c r="B223" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C223" t="str">
         <f t="shared" si="3"/>
@@ -5723,7 +5738,7 @@
     </row>
     <row r="224" spans="2:5">
       <c r="B224" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C224" t="str">
         <f t="shared" si="3"/>
@@ -5738,7 +5753,7 @@
     </row>
     <row r="225" spans="2:5">
       <c r="B225" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C225" t="str">
         <f t="shared" si="3"/>
@@ -5753,7 +5768,7 @@
     </row>
     <row r="226" spans="2:5">
       <c r="B226" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C226" t="str">
         <f t="shared" si="3"/>
@@ -5768,7 +5783,7 @@
     </row>
     <row r="227" spans="2:5">
       <c r="B227" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C227" t="str">
         <f t="shared" si="3"/>
@@ -5783,7 +5798,7 @@
     </row>
     <row r="228" spans="2:5">
       <c r="B228" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C228" t="str">
         <f t="shared" si="3"/>
@@ -5798,7 +5813,7 @@
     </row>
     <row r="229" spans="2:5">
       <c r="B229" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C229" t="str">
         <f t="shared" si="3"/>
@@ -5813,7 +5828,7 @@
     </row>
     <row r="230" spans="2:5">
       <c r="B230" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C230" t="str">
         <f t="shared" si="3"/>
@@ -5828,7 +5843,7 @@
     </row>
     <row r="231" spans="2:5">
       <c r="B231" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C231" t="str">
         <f t="shared" si="3"/>
@@ -5843,7 +5858,7 @@
     </row>
     <row r="232" spans="2:5">
       <c r="B232" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C232" t="str">
         <f t="shared" si="3"/>
@@ -5858,7 +5873,7 @@
     </row>
     <row r="233" spans="2:5">
       <c r="B233" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C233" t="str">
         <f t="shared" si="3"/>
@@ -5873,7 +5888,7 @@
     </row>
     <row r="234" spans="2:5">
       <c r="B234" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C234" t="str">
         <f t="shared" si="3"/>
@@ -5888,7 +5903,7 @@
     </row>
     <row r="235" spans="2:5">
       <c r="B235" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C235" t="str">
         <f t="shared" si="3"/>
@@ -5903,7 +5918,7 @@
     </row>
     <row r="236" spans="2:5">
       <c r="B236" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C236" t="str">
         <f t="shared" si="3"/>
@@ -5918,7 +5933,7 @@
     </row>
     <row r="237" spans="2:5">
       <c r="B237" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C237" t="str">
         <f t="shared" si="3"/>
@@ -5933,7 +5948,7 @@
     </row>
     <row r="238" spans="2:5">
       <c r="B238" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C238" t="str">
         <f t="shared" si="3"/>
@@ -5948,7 +5963,7 @@
     </row>
     <row r="239" spans="2:5">
       <c r="B239" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C239" t="str">
         <f t="shared" si="3"/>
@@ -5963,7 +5978,7 @@
     </row>
     <row r="240" spans="2:5">
       <c r="B240" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C240" t="str">
         <f t="shared" si="3"/>
@@ -5978,7 +5993,7 @@
     </row>
     <row r="241" spans="2:5">
       <c r="B241" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C241" t="str">
         <f t="shared" si="3"/>
@@ -5993,7 +6008,7 @@
     </row>
     <row r="242" spans="2:5">
       <c r="B242" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C242" t="str">
         <f t="shared" si="3"/>
@@ -6008,7 +6023,7 @@
     </row>
     <row r="243" spans="2:5">
       <c r="B243" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C243" t="str">
         <f t="shared" si="3"/>
@@ -6023,7 +6038,7 @@
     </row>
     <row r="244" spans="2:5">
       <c r="B244" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C244" t="str">
         <f t="shared" si="3"/>
@@ -6038,7 +6053,7 @@
     </row>
     <row r="245" spans="2:5">
       <c r="B245" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C245" t="str">
         <f t="shared" si="3"/>
@@ -6053,7 +6068,7 @@
     </row>
     <row r="246" spans="2:5">
       <c r="B246" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C246" t="str">
         <f t="shared" si="3"/>
@@ -6068,7 +6083,7 @@
     </row>
     <row r="247" spans="2:5">
       <c r="B247" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C247" t="str">
         <f t="shared" si="3"/>
@@ -6083,7 +6098,7 @@
     </row>
     <row r="248" spans="2:5">
       <c r="B248" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C248" t="str">
         <f t="shared" si="3"/>
@@ -6098,7 +6113,7 @@
     </row>
     <row r="249" spans="2:5">
       <c r="B249" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C249" t="str">
         <f t="shared" si="3"/>
@@ -6113,7 +6128,7 @@
     </row>
     <row r="250" spans="2:5">
       <c r="B250" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C250" t="str">
         <f t="shared" si="3"/>
@@ -6128,7 +6143,7 @@
     </row>
     <row r="251" spans="2:5">
       <c r="B251" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C251" t="str">
         <f t="shared" si="3"/>
@@ -6143,7 +6158,7 @@
     </row>
     <row r="252" spans="2:5">
       <c r="B252" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C252" t="str">
         <f t="shared" si="3"/>
@@ -6158,7 +6173,7 @@
     </row>
     <row r="253" spans="2:5">
       <c r="B253" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C253" t="str">
         <f t="shared" si="3"/>
@@ -6173,7 +6188,7 @@
     </row>
     <row r="254" spans="2:5">
       <c r="B254" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C254" t="str">
         <f t="shared" si="3"/>
@@ -6188,7 +6203,7 @@
     </row>
     <row r="255" spans="2:5">
       <c r="B255" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C255" t="str">
         <f t="shared" si="3"/>
@@ -6203,7 +6218,7 @@
     </row>
     <row r="256" spans="2:5">
       <c r="B256" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C256" t="str">
         <f t="shared" si="3"/>
@@ -6218,7 +6233,7 @@
     </row>
     <row r="257" spans="2:5">
       <c r="B257" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C257" t="str">
         <f t="shared" si="3"/>
@@ -6233,7 +6248,7 @@
     </row>
     <row r="258" spans="2:5">
       <c r="B258" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C258" t="str">
         <f t="shared" si="3"/>
@@ -6248,7 +6263,7 @@
     </row>
     <row r="259" spans="2:5">
       <c r="B259" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C259" t="str">
         <f t="shared" si="3"/>
@@ -6263,7 +6278,7 @@
     </row>
     <row r="260" spans="2:5">
       <c r="B260" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C260" t="str">
         <f t="shared" si="3"/>
@@ -6278,7 +6293,7 @@
     </row>
     <row r="261" spans="2:5">
       <c r="B261" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C261" t="str">
         <f t="shared" si="3"/>
@@ -6293,7 +6308,7 @@
     </row>
     <row r="262" spans="2:5">
       <c r="B262" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C262" t="str">
         <f t="shared" si="3"/>
@@ -6308,7 +6323,7 @@
     </row>
     <row r="263" spans="2:5">
       <c r="B263" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C263" t="str">
         <f t="shared" si="3"/>
@@ -6323,7 +6338,7 @@
     </row>
     <row r="264" spans="2:5">
       <c r="B264" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C264" t="str">
         <f t="shared" si="3"/>
@@ -6338,7 +6353,7 @@
     </row>
     <row r="265" spans="2:5">
       <c r="B265" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C265" t="str">
         <f t="shared" si="3"/>
@@ -6353,7 +6368,7 @@
     </row>
     <row r="266" spans="2:5">
       <c r="B266" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C266" t="str">
         <f t="shared" si="3"/>
@@ -6368,7 +6383,7 @@
     </row>
     <row r="267" spans="2:5">
       <c r="B267" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C267" t="str">
         <f t="shared" si="3"/>
@@ -6383,7 +6398,7 @@
     </row>
     <row r="268" spans="2:5">
       <c r="B268" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C268" t="str">
         <f t="shared" si="3"/>
@@ -6398,7 +6413,7 @@
     </row>
     <row r="269" spans="2:5">
       <c r="B269" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C269" t="str">
         <f t="shared" si="3"/>
@@ -6413,7 +6428,7 @@
     </row>
     <row r="270" spans="2:5">
       <c r="B270" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C270" t="str">
         <f t="shared" si="3"/>
@@ -6428,7 +6443,7 @@
     </row>
     <row r="271" spans="2:5">
       <c r="B271" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C271" t="str">
         <f t="shared" si="3"/>
@@ -6443,7 +6458,7 @@
     </row>
     <row r="272" spans="2:5">
       <c r="B272" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C272" t="str">
         <f t="shared" si="3"/>
@@ -6458,7 +6473,7 @@
     </row>
     <row r="273" spans="2:5">
       <c r="B273" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C273" t="str">
         <f t="shared" si="3"/>
@@ -6473,7 +6488,7 @@
     </row>
     <row r="274" spans="2:5">
       <c r="B274" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C274" t="str">
         <f t="shared" si="3"/>
@@ -6488,7 +6503,7 @@
     </row>
     <row r="275" spans="2:5">
       <c r="B275" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C275" t="str">
         <f t="shared" si="3"/>
@@ -6503,7 +6518,7 @@
     </row>
     <row r="276" spans="2:5">
       <c r="B276" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C276" t="str">
         <f t="shared" si="3"/>
@@ -6518,7 +6533,7 @@
     </row>
     <row r="277" spans="2:5">
       <c r="B277" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C277" t="str">
         <f t="shared" si="3"/>
@@ -6533,7 +6548,7 @@
     </row>
     <row r="278" spans="2:5">
       <c r="B278" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C278" t="str">
         <f t="shared" ref="C278:C321" si="4">$C$3</f>
@@ -6548,7 +6563,7 @@
     </row>
     <row r="279" spans="2:5">
       <c r="B279" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C279" t="str">
         <f t="shared" si="4"/>
@@ -6563,7 +6578,7 @@
     </row>
     <row r="280" spans="2:5">
       <c r="B280" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C280" t="str">
         <f t="shared" si="4"/>
@@ -6578,7 +6593,7 @@
     </row>
     <row r="281" spans="2:5">
       <c r="B281" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C281" t="str">
         <f t="shared" si="4"/>
@@ -6593,7 +6608,7 @@
     </row>
     <row r="282" spans="2:5">
       <c r="B282" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C282" t="str">
         <f t="shared" si="4"/>
@@ -6608,7 +6623,7 @@
     </row>
     <row r="283" spans="2:5">
       <c r="B283" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C283" t="str">
         <f t="shared" si="4"/>
@@ -6623,7 +6638,7 @@
     </row>
     <row r="284" spans="2:5">
       <c r="B284" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C284" t="str">
         <f t="shared" si="4"/>
@@ -6638,7 +6653,7 @@
     </row>
     <row r="285" spans="2:5">
       <c r="B285" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C285" t="str">
         <f t="shared" si="4"/>
@@ -6653,7 +6668,7 @@
     </row>
     <row r="286" spans="2:5">
       <c r="B286" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C286" t="str">
         <f t="shared" si="4"/>
@@ -6668,7 +6683,7 @@
     </row>
     <row r="287" spans="2:5">
       <c r="B287" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C287" t="str">
         <f t="shared" si="4"/>
@@ -6683,7 +6698,7 @@
     </row>
     <row r="288" spans="2:5">
       <c r="B288" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C288" t="str">
         <f t="shared" si="4"/>
@@ -6698,7 +6713,7 @@
     </row>
     <row r="289" spans="2:5">
       <c r="B289" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C289" t="str">
         <f t="shared" si="4"/>
@@ -6713,7 +6728,7 @@
     </row>
     <row r="290" spans="2:5">
       <c r="B290" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C290" t="str">
         <f t="shared" si="4"/>
@@ -6728,7 +6743,7 @@
     </row>
     <row r="291" spans="2:5">
       <c r="B291" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C291" t="str">
         <f t="shared" si="4"/>
@@ -6743,7 +6758,7 @@
     </row>
     <row r="292" spans="2:5">
       <c r="B292" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C292" t="str">
         <f t="shared" si="4"/>
@@ -6758,7 +6773,7 @@
     </row>
     <row r="293" spans="2:5">
       <c r="B293" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C293" t="str">
         <f t="shared" si="4"/>
@@ -6773,7 +6788,7 @@
     </row>
     <row r="294" spans="2:5">
       <c r="B294" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C294" t="str">
         <f t="shared" si="4"/>
@@ -6788,7 +6803,7 @@
     </row>
     <row r="295" spans="2:5">
       <c r="B295" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C295" t="str">
         <f t="shared" si="4"/>
@@ -6803,7 +6818,7 @@
     </row>
     <row r="296" spans="2:5">
       <c r="B296" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C296" t="str">
         <f t="shared" si="4"/>
@@ -6818,7 +6833,7 @@
     </row>
     <row r="297" spans="2:5">
       <c r="B297" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C297" t="str">
         <f t="shared" si="4"/>
@@ -6833,7 +6848,7 @@
     </row>
     <row r="298" spans="2:5">
       <c r="B298" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C298" t="str">
         <f t="shared" si="4"/>
@@ -6848,7 +6863,7 @@
     </row>
     <row r="299" spans="2:5">
       <c r="B299" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C299" t="str">
         <f t="shared" si="4"/>
@@ -6863,7 +6878,7 @@
     </row>
     <row r="300" spans="2:5">
       <c r="B300" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C300" t="str">
         <f t="shared" si="4"/>
@@ -6878,7 +6893,7 @@
     </row>
     <row r="301" spans="2:5">
       <c r="B301" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C301" t="str">
         <f t="shared" si="4"/>
@@ -6893,7 +6908,7 @@
     </row>
     <row r="302" spans="2:5">
       <c r="B302" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C302" t="str">
         <f t="shared" si="4"/>
@@ -6908,7 +6923,7 @@
     </row>
     <row r="303" spans="2:5">
       <c r="B303" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C303" t="str">
         <f t="shared" si="4"/>
@@ -6923,7 +6938,7 @@
     </row>
     <row r="304" spans="2:5">
       <c r="B304" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C304" t="str">
         <f t="shared" si="4"/>
@@ -6938,7 +6953,7 @@
     </row>
     <row r="305" spans="2:5">
       <c r="B305" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C305" t="str">
         <f t="shared" si="4"/>
@@ -6953,7 +6968,7 @@
     </row>
     <row r="306" spans="2:5">
       <c r="B306" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C306" t="str">
         <f t="shared" si="4"/>
@@ -6968,7 +6983,7 @@
     </row>
     <row r="307" spans="2:5">
       <c r="B307" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C307" t="str">
         <f t="shared" si="4"/>
@@ -6983,7 +6998,7 @@
     </row>
     <row r="308" spans="2:5">
       <c r="B308" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C308" t="str">
         <f t="shared" si="4"/>
@@ -6998,7 +7013,7 @@
     </row>
     <row r="309" spans="2:5">
       <c r="B309" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C309" t="str">
         <f t="shared" si="4"/>
@@ -7013,7 +7028,7 @@
     </row>
     <row r="310" spans="2:5">
       <c r="B310" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C310" t="str">
         <f t="shared" si="4"/>
@@ -7028,7 +7043,7 @@
     </row>
     <row r="311" spans="2:5">
       <c r="B311" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C311" t="str">
         <f t="shared" si="4"/>
@@ -7043,7 +7058,7 @@
     </row>
     <row r="312" spans="2:5">
       <c r="B312" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C312" t="str">
         <f t="shared" si="4"/>
@@ -7058,7 +7073,7 @@
     </row>
     <row r="313" spans="2:5">
       <c r="B313" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C313" t="str">
         <f t="shared" si="4"/>
@@ -7073,7 +7088,7 @@
     </row>
     <row r="314" spans="2:5">
       <c r="B314" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C314" t="str">
         <f t="shared" si="4"/>
@@ -7088,7 +7103,7 @@
     </row>
     <row r="315" spans="2:5">
       <c r="B315" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C315" t="str">
         <f t="shared" si="4"/>
@@ -7103,7 +7118,7 @@
     </row>
     <row r="316" spans="2:5">
       <c r="B316" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C316" t="str">
         <f t="shared" si="4"/>
@@ -7118,7 +7133,7 @@
     </row>
     <row r="317" spans="2:5">
       <c r="B317" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C317" t="str">
         <f t="shared" si="4"/>
@@ -7133,7 +7148,7 @@
     </row>
     <row r="318" spans="2:5">
       <c r="B318" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C318" t="str">
         <f t="shared" si="4"/>
@@ -7148,7 +7163,7 @@
     </row>
     <row r="319" spans="2:5">
       <c r="B319" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C319" t="str">
         <f t="shared" si="4"/>
@@ -7163,7 +7178,7 @@
     </row>
     <row r="320" spans="2:5">
       <c r="B320" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C320" t="str">
         <f t="shared" si="4"/>
@@ -7178,7 +7193,7 @@
     </row>
     <row r="321" spans="2:5">
       <c r="B321" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C321" t="str">
         <f t="shared" si="4"/>
